--- a/marsu-pwa-dashboard/py_scripts/dashboard-ds.xlsx
+++ b/marsu-pwa-dashboard/py_scripts/dashboard-ds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HungryCoder\Desktop\ds-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\marsu-dasboard-rev2\marsu-pwa-dashboard\py_scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1EA469-894E-4694-A62D-50C29A6A37B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABD1A72-78A6-4A97-8F19-629C7CC8CD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{478613E3-41A5-43DD-B682-B6E5AE29BE39}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{478613E3-41A5-43DD-B682-B6E5AE29BE39}"/>
   </bookViews>
   <sheets>
     <sheet name="enrollment_rate_undergraduate" sheetId="1" r:id="rId1"/>
@@ -7754,7 +7754,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="mmm&quot;-&quot;dd&quot;-&quot;yyyy"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -7852,7 +7852,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -7867,61 +7867,59 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12980,10 +12978,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8B2FA63-F2AB-4AD3-8B17-9196A9E1DD8B}">
-  <dimension ref="A1:G1152"/>
+  <dimension ref="A1:F1152"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="65.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.42578125" customWidth="1"/>
     <col min="5" max="5" width="18.42578125" customWidth="1"/>
     <col min="6" max="6" width="20.28515625" customWidth="1"/>
   </cols>
@@ -26801,7 +26799,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="1089" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1089" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1089" t="s">
         <v>1833</v>
       </c>
@@ -26815,7 +26813,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="1090" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1090" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1090" t="s">
         <v>1833</v>
       </c>
@@ -26829,7 +26827,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="1091" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1091" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1091" t="s">
         <v>1833</v>
       </c>
@@ -26840,7 +26838,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="1092" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1092" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1092" t="s">
         <v>1833</v>
       </c>
@@ -26854,7 +26852,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="1093" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1093" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1093" t="s">
         <v>1833</v>
       </c>
@@ -26868,7 +26866,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="1094" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="1094" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C1094" t="s">
         <v>1833</v>
       </c>
@@ -26882,563 +26880,563 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="1095" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1095" t="s">
+    <row r="1095" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1095" t="s">
         <v>1834</v>
       </c>
-      <c r="D1095" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1095" t="s">
+      <c r="E1095" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1095" t="s">
         <v>1835</v>
       </c>
     </row>
-    <row r="1096" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1096" t="s">
+    <row r="1096" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1096" t="s">
         <v>1836</v>
       </c>
-      <c r="D1096" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1096" t="s">
+      <c r="E1096" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1096" t="s">
         <v>1837</v>
       </c>
     </row>
-    <row r="1097" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1097" t="s">
+    <row r="1097" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1097" t="s">
         <v>1838</v>
       </c>
-      <c r="D1097" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1097" t="s">
+      <c r="E1097" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1097" t="s">
         <v>1422</v>
       </c>
     </row>
-    <row r="1098" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1098" t="s">
+    <row r="1098" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1098" t="s">
         <v>1839</v>
       </c>
-      <c r="D1098" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1098" t="s">
+      <c r="E1098" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1098" t="s">
         <v>1840</v>
       </c>
     </row>
-    <row r="1099" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1099" t="s">
+    <row r="1099" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1099" t="s">
         <v>1841</v>
       </c>
-      <c r="D1099" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1099" t="s">
+      <c r="E1099" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1099" t="s">
         <v>1840</v>
       </c>
     </row>
-    <row r="1100" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1100" t="s">
+    <row r="1100" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1100" t="s">
         <v>1842</v>
       </c>
-      <c r="D1100" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1100" t="s">
+      <c r="E1100" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1100" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="1101" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1101" t="s">
+    <row r="1101" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1101" t="s">
         <v>1843</v>
       </c>
-      <c r="D1101" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1102" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1102" t="s">
+      <c r="E1101" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1102" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1102" t="s">
         <v>1844</v>
       </c>
-      <c r="D1102" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1102" t="s">
+      <c r="E1102" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1102" t="s">
         <v>1845</v>
       </c>
     </row>
-    <row r="1103" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1103" t="s">
+    <row r="1103" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1103" t="s">
         <v>1846</v>
       </c>
-      <c r="D1103" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1103" t="s">
+      <c r="E1103" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1103" t="s">
         <v>1847</v>
       </c>
     </row>
-    <row r="1104" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1104" t="s">
+    <row r="1104" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D1104" t="s">
         <v>1848</v>
       </c>
-      <c r="D1104" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1105" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1105" t="s">
+      <c r="E1104" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1105" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1105" t="s">
         <v>1849</v>
       </c>
-      <c r="D1105" t="s">
-        <v>195</v>
-      </c>
-      <c r="G1105" t="s">
+      <c r="E1105" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1105" t="s">
         <v>1850</v>
       </c>
     </row>
-    <row r="1106" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1106" t="s">
+    <row r="1106" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1106" t="s">
         <v>1851</v>
       </c>
-      <c r="D1106" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1106" t="s">
+      <c r="E1106" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1106" t="s">
         <v>1852</v>
       </c>
     </row>
-    <row r="1107" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1107" t="s">
+    <row r="1107" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1107" t="s">
         <v>1853</v>
       </c>
-      <c r="D1107" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1107" t="s">
+      <c r="E1107" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1107" t="s">
         <v>1551</v>
       </c>
     </row>
-    <row r="1108" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1108" t="s">
+    <row r="1108" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1108" t="s">
         <v>1854</v>
       </c>
-      <c r="D1108" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1109" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1109" t="s">
+      <c r="E1108" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1109" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1109" t="s">
         <v>1855</v>
       </c>
-      <c r="D1109" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1109" t="s">
+      <c r="E1109" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1109" t="s">
         <v>1852</v>
       </c>
     </row>
-    <row r="1110" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1110" t="s">
+    <row r="1110" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1110" t="s">
         <v>1856</v>
       </c>
-      <c r="D1110" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1111" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1111" t="s">
+      <c r="E1110" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1111" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1111" t="s">
         <v>1857</v>
       </c>
-      <c r="D1111" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1111" t="s">
+      <c r="E1111" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1111" t="s">
         <v>1852</v>
       </c>
     </row>
-    <row r="1112" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1112" t="s">
+    <row r="1112" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1112" t="s">
         <v>1858</v>
       </c>
-      <c r="D1112" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1113" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1113" t="s">
+      <c r="E1112" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1113" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1113" t="s">
         <v>1859</v>
       </c>
-      <c r="D1113" t="s">
+      <c r="E1113" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1114" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1114" t="s">
+    <row r="1114" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1114" t="s">
         <v>1860</v>
       </c>
-      <c r="D1114" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1114" t="s">
+      <c r="E1114" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1114" t="s">
         <v>1861</v>
       </c>
     </row>
-    <row r="1115" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1115" t="s">
+    <row r="1115" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1115" t="s">
         <v>1862</v>
       </c>
-      <c r="D1115" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1115" t="s">
+      <c r="E1115" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1115" t="s">
         <v>1863</v>
       </c>
     </row>
-    <row r="1116" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1116" t="s">
+    <row r="1116" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1116" t="s">
         <v>1864</v>
       </c>
-      <c r="D1116" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1116" t="s">
+      <c r="E1116" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1116" t="s">
         <v>1422</v>
       </c>
     </row>
-    <row r="1117" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1117" t="s">
+    <row r="1117" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1117" t="s">
         <v>1865</v>
       </c>
-      <c r="D1117" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1118" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1118" t="s">
+      <c r="E1117" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1118" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1118" t="s">
         <v>1866</v>
       </c>
-      <c r="D1118" t="s">
+      <c r="E1118" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1119" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1119" t="s">
+    <row r="1119" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1119" t="s">
         <v>1867</v>
       </c>
-      <c r="D1119" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1119" t="s">
+      <c r="E1119" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1119" t="s">
         <v>1868</v>
       </c>
     </row>
-    <row r="1120" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1120" t="s">
+    <row r="1120" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1120" t="s">
         <v>1869</v>
       </c>
-      <c r="D1120" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1120" t="s">
+      <c r="E1120" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1120" t="s">
         <v>1870</v>
       </c>
     </row>
-    <row r="1121" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1121" t="s">
+    <row r="1121" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1121" t="s">
         <v>1871</v>
       </c>
-      <c r="D1121" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1121" t="s">
+      <c r="E1121" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1121" t="s">
         <v>1872</v>
       </c>
     </row>
-    <row r="1122" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1122" t="s">
+    <row r="1122" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1122" t="s">
         <v>1873</v>
       </c>
-      <c r="D1122" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1122" t="s">
+      <c r="E1122" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1122" t="s">
         <v>1551</v>
       </c>
     </row>
-    <row r="1123" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1123" t="s">
+    <row r="1123" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1123" t="s">
         <v>1874</v>
       </c>
-      <c r="D1123" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1123" t="s">
+      <c r="E1123" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1123" t="s">
         <v>1875</v>
       </c>
     </row>
-    <row r="1124" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1124" t="s">
+    <row r="1124" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1124" t="s">
         <v>1876</v>
       </c>
-      <c r="D1124" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1124" t="s">
+      <c r="E1124" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1124" t="s">
         <v>1877</v>
       </c>
     </row>
-    <row r="1125" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1125" t="s">
+    <row r="1125" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1125" t="s">
         <v>1878</v>
       </c>
-      <c r="D1125" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1125" t="s">
+      <c r="E1125" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1125" t="s">
         <v>1551</v>
       </c>
     </row>
-    <row r="1126" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1126" t="s">
+    <row r="1126" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1126" t="s">
         <v>1879</v>
       </c>
-      <c r="D1126" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1126" t="s">
+      <c r="E1126" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1126" t="s">
         <v>1880</v>
       </c>
     </row>
-    <row r="1127" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1127" t="s">
+    <row r="1127" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1127" t="s">
         <v>1881</v>
       </c>
-      <c r="D1127" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1128" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1128" t="s">
+      <c r="E1127" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1128" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1128" t="s">
         <v>1882</v>
       </c>
-      <c r="D1128" t="s">
+      <c r="E1128" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1129" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1129" t="s">
+    <row r="1129" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1129" t="s">
         <v>1883</v>
       </c>
-      <c r="D1129" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1129" t="s">
+      <c r="E1129" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1129" t="s">
         <v>1884</v>
       </c>
     </row>
-    <row r="1130" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1130" t="s">
+    <row r="1130" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1130" t="s">
         <v>1885</v>
       </c>
-      <c r="D1130" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1131" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1131" t="s">
+      <c r="E1130" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1131" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1131" t="s">
         <v>1886</v>
       </c>
-      <c r="D1131" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1131" t="s">
+      <c r="E1131" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1131" t="s">
         <v>1887</v>
       </c>
     </row>
-    <row r="1132" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1132" t="s">
+    <row r="1132" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1132" t="s">
         <v>1888</v>
       </c>
-      <c r="D1132" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1133" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1133" t="s">
+      <c r="E1132" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1133" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1133" t="s">
         <v>1889</v>
       </c>
-      <c r="D1133" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1133" t="s">
+      <c r="E1133" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1133" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="1134" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1134" t="s">
+    <row r="1134" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1134" t="s">
         <v>1891</v>
       </c>
-      <c r="D1134" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1135" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1135" t="s">
+      <c r="E1134" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1135" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1135" t="s">
         <v>1892</v>
       </c>
-      <c r="D1135" t="s">
+      <c r="E1135" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1136" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1136" t="s">
+    <row r="1136" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1136" t="s">
         <v>1893</v>
       </c>
-      <c r="D1136" t="s">
+      <c r="E1136" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1137" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1137" t="s">
+    <row r="1137" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1137" t="s">
         <v>1894</v>
       </c>
-      <c r="D1137" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1137" t="s">
+      <c r="E1137" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1137" t="s">
         <v>1895</v>
       </c>
     </row>
-    <row r="1138" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1138" t="s">
+    <row r="1138" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1138" t="s">
         <v>1896</v>
       </c>
-      <c r="D1138" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1139" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1139" t="s">
+      <c r="E1138" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1139" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1139" t="s">
         <v>1897</v>
       </c>
-      <c r="D1139" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1139" t="s">
+      <c r="E1139" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1139" t="s">
         <v>1898</v>
       </c>
     </row>
-    <row r="1140" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1140" t="s">
+    <row r="1140" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1140" t="s">
         <v>1899</v>
       </c>
-      <c r="D1140" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1141" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1141" t="s">
+      <c r="E1140" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1141" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1141" t="s">
         <v>1900</v>
       </c>
-      <c r="D1141" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1141" t="s">
+      <c r="E1141" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1141" t="s">
         <v>1901</v>
       </c>
     </row>
-    <row r="1142" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1142" t="s">
+    <row r="1142" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1142" t="s">
         <v>1902</v>
       </c>
-      <c r="D1142" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1143" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1143" t="s">
+      <c r="E1142" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1143" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1143" t="s">
         <v>1903</v>
       </c>
-      <c r="D1143" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1143" t="s">
+      <c r="E1143" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1143" t="s">
         <v>1904</v>
       </c>
     </row>
-    <row r="1144" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1144" t="s">
+    <row r="1144" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1144" t="s">
         <v>1905</v>
       </c>
-      <c r="D1144" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1145" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1145" t="s">
+      <c r="E1144" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1145" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1145" t="s">
         <v>1906</v>
       </c>
-      <c r="D1145" t="s">
-        <v>190</v>
-      </c>
-      <c r="G1145" t="s">
+      <c r="E1145" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1145" t="s">
         <v>1907</v>
       </c>
     </row>
-    <row r="1146" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1146" t="s">
+    <row r="1146" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1146" t="s">
         <v>1908</v>
       </c>
-      <c r="D1146" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1147" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1147" t="s">
+      <c r="E1146" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1147" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1147" t="s">
         <v>1909</v>
       </c>
-      <c r="D1147" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1148" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1148" t="s">
+      <c r="E1147" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1148" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1148" t="s">
         <v>1910</v>
       </c>
-      <c r="D1148" t="s">
+      <c r="E1148" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1149" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1149" t="s">
+    <row r="1149" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1149" t="s">
         <v>1911</v>
       </c>
-      <c r="D1149" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="1150" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1150" t="s">
+      <c r="E1149" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1150" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1150" t="s">
         <v>1912</v>
       </c>
-      <c r="D1150" t="s">
+      <c r="E1150" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1151" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1151" t="s">
+    <row r="1151" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1151" t="s">
         <v>1913</v>
       </c>
-      <c r="D1151" t="s">
+      <c r="E1151" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="1152" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C1152" t="s">
+    <row r="1152" spans="4:6" x14ac:dyDescent="0.25">
+      <c r="D1152" t="s">
         <v>1914</v>
       </c>
-      <c r="D1152" t="s">
+      <c r="E1152" t="s">
         <v>195</v>
       </c>
     </row>
@@ -27466,5790 +27464,5790 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" t="s">
         <v>1940</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" t="s">
         <v>1941</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" t="s">
         <v>1942</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>1943</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>1944</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" t="s">
         <v>1945</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" t="s">
         <v>1946</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" t="s">
         <v>1947</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="6" t="s">
         <v>1948</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2">
         <v>2023</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>1949</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>1950</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="9">
         <v>44850</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="9">
         <v>44941</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>1952</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>1953</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="10">
         <v>44966</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3">
         <v>2023</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>1955</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>1956</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <v>44829</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="9">
         <v>44951</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="7" t="s">
         <v>1957</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>1958</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>1959</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4">
         <v>2023</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="7" t="s">
         <v>1960</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>1961</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="9">
         <v>44835</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>44986</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>1962</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="7" t="s">
         <v>1963</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>1965</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5">
         <v>2023</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="7" t="s">
         <v>1966</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>1967</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="9">
         <v>44621</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <v>44987</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>1962</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="7" t="s">
         <v>1963</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>1965</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6">
         <v>2023</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="7" t="s">
         <v>1968</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>1969</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="9">
         <v>44866</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="9">
         <v>45017</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="7" t="s">
         <v>1970</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="7" t="s">
         <v>1971</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="10" t="s">
         <v>1972</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7">
         <v>2023</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="7" t="s">
         <v>1973</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>1974</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="9">
         <v>44850</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <v>44941</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>1975</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="7" t="s">
         <v>1976</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="10" t="s">
         <v>1977</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8">
         <v>2023</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>1978</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>1979</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="9" t="s">
         <v>1980</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
         <v>1981</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>1982</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="7" t="s">
         <v>1983</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="10" t="s">
         <v>1984</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9">
         <v>2023</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="7" t="s">
         <v>1985</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>1986</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="9" t="s">
         <v>1987</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>1988</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="7" t="s">
         <v>1989</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="7" t="s">
         <v>1990</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="10" t="s">
         <v>1991</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10">
         <v>2023</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="7" t="s">
         <v>1992</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>1993</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>1994</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>44931</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>1995</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="7" t="s">
         <v>1996</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="10" t="s">
         <v>1997</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11">
         <v>2023</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="7" t="s">
         <v>1998</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="7" t="s">
         <v>1999</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="9" t="s">
         <v>2000</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>2001</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="7" t="s">
         <v>2002</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="7" t="s">
         <v>1996</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="10" t="s">
         <v>1997</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12">
         <v>2023</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>2003</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="7" t="s">
         <v>2004</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>45047</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="12" t="s">
         <v>2005</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>2006</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="7" t="s">
         <v>2007</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="10" t="s">
         <v>2008</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13">
         <v>2023</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>2009</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>1974</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>2010</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="12" t="s">
         <v>2011</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="7" t="s">
         <v>2012</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="7" t="s">
         <v>2013</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>2014</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14">
         <v>2023</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>2015</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>2016</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="12">
         <v>44567</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="12">
         <v>44932</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>2017</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>2018</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="10" t="s">
         <v>2019</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15">
         <v>2023</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>2020</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="7" t="s">
         <v>2021</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>2022</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="12" t="s">
         <v>2023</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="7" t="s">
         <v>2024</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="7" t="s">
         <v>2025</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="10" t="s">
         <v>2026</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16">
         <v>2023</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>2027</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>2028</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="9">
         <v>45047</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="9">
         <v>45051</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="7" t="s">
         <v>2024</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="7" t="s">
         <v>2029</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="10" t="s">
         <v>2026</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17">
         <v>2023</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>2030</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>2016</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <v>44570</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="12">
         <v>44932</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="7" t="s">
         <v>2031</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="7" t="s">
         <v>2032</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="10" t="s">
         <v>2033</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18">
         <v>2023</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>2034</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="7" t="s">
         <v>2035</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="13" t="s">
         <v>1994</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="13" t="s">
         <v>2011</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19">
         <v>2023</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>2040</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="7" t="s">
         <v>2041</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="13" t="s">
         <v>2042</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="13" t="s">
         <v>1981</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20">
         <v>2023</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="7" t="s">
         <v>2043</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="7" t="s">
         <v>2044</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="13" t="s">
         <v>1994</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="13" t="s">
         <v>2011</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21">
         <v>2023</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="7" t="s">
         <v>2045</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="7" t="s">
         <v>2046</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="13" t="s">
         <v>2042</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="13" t="s">
         <v>1981</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22">
         <v>2023</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="7" t="s">
         <v>2047</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="7" t="s">
         <v>2048</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="13">
         <v>45201</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="13">
         <v>45204</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23">
         <v>2023</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="7" t="s">
         <v>2049</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>2050</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="13" t="s">
         <v>2042</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="13" t="s">
         <v>1981</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24">
         <v>2023</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="7" t="s">
         <v>2051</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>2052</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="13" t="s">
         <v>1994</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="13" t="s">
         <v>2011</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25">
         <v>2023</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="7" t="s">
         <v>2053</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>2054</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="13" t="s">
         <v>2055</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="13" t="s">
         <v>2001</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26">
         <v>2023</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>2056</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>2057</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="13" t="s">
         <v>2058</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="13" t="s">
         <v>2059</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27">
         <v>2023</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="7" t="s">
         <v>2060</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>2061</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="13" t="s">
         <v>2062</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="13" t="s">
         <v>2063</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28">
         <v>2023</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="7" t="s">
         <v>2064</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>2065</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="13">
         <v>45200</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="13">
         <v>45205</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29">
         <v>2023</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="7" t="s">
         <v>2066</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>2067</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="13" t="s">
         <v>2023</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="13" t="s">
         <v>2068</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30">
         <v>2023</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="7" t="s">
         <v>2069</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>2067</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="13" t="s">
         <v>2011</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="13" t="s">
         <v>2068</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="7" t="s">
         <v>2036</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="7" t="s">
         <v>2037</v>
       </c>
-      <c r="I30" s="10" t="s">
+      <c r="I30" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="10" t="s">
         <v>2039</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31">
         <v>2023</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="7" t="s">
         <v>2070</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>2071</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="9">
         <v>44929</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="9">
         <v>44934</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="7" t="s">
         <v>2072</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="7" t="s">
         <v>2073</v>
       </c>
-      <c r="I31" s="10" t="s">
+      <c r="I31" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="10" t="s">
         <v>2074</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32">
         <v>2023</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="7" t="s">
         <v>2075</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>2076</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="14" t="s">
         <v>2077</v>
       </c>
-      <c r="F32" s="16" t="s">
+      <c r="F32" s="14" t="s">
         <v>2078</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="7" t="s">
         <v>2079</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="7" t="s">
         <v>2080</v>
       </c>
-      <c r="I32" s="10" t="s">
+      <c r="I32" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="10" t="s">
         <v>2081</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
+      <c r="A33">
         <v>2023</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="7" t="s">
         <v>2082</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>2083</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="14">
         <v>44571</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="14">
         <v>44935</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="7" t="s">
         <v>2084</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="7" t="s">
         <v>2085</v>
       </c>
-      <c r="I33" s="10" t="s">
+      <c r="I33" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="10">
         <v>45224</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="A34">
         <v>2023</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="7" t="s">
         <v>2086</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>2087</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="14" t="s">
         <v>2001</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="14" t="s">
         <v>2088</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="7" t="s">
         <v>2089</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="7" t="s">
         <v>2090</v>
       </c>
-      <c r="I34" s="10" t="s">
+      <c r="I34" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J34" s="12" t="s">
+      <c r="J34" s="10" t="s">
         <v>2091</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
+      <c r="A35">
         <v>2023</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="7" t="s">
         <v>2092</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>2093</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E35" s="16">
+      <c r="E35" s="14">
         <v>44930</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="14">
         <v>44935</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="7" t="s">
         <v>2094</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="7" t="s">
         <v>2095</v>
       </c>
-      <c r="I35" s="10" t="s">
+      <c r="I35" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J35" s="12" t="s">
+      <c r="J35" s="10" t="s">
         <v>2096</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
+      <c r="A36">
         <v>2023</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="7" t="s">
         <v>2097</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="7" t="s">
         <v>2098</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E36" s="16">
+      <c r="E36" s="14">
         <v>45054</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="14">
         <v>45057</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>2094</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="7" t="s">
         <v>2095</v>
       </c>
-      <c r="I36" s="10" t="s">
+      <c r="I36" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="J36" s="10" t="s">
         <v>2096</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
+      <c r="A37">
         <v>2023</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="7" t="s">
         <v>2099</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="7" t="s">
         <v>2100</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E37" s="16">
+      <c r="E37" s="14">
         <v>45054</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="14">
         <v>45057</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="7" t="s">
         <v>2094</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="7" t="s">
         <v>2101</v>
       </c>
-      <c r="I37" s="10" t="s">
+      <c r="I37" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J37" s="12" t="s">
+      <c r="J37" s="10" t="s">
         <v>2096</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
+      <c r="A38">
         <v>2023</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="7" t="s">
         <v>2102</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="7" t="s">
         <v>2103</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E38" s="16">
+      <c r="E38" s="14">
         <v>45053</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="14">
         <v>45057</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="7" t="s">
         <v>2094</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="7" t="s">
         <v>2101</v>
       </c>
-      <c r="I38" s="10" t="s">
+      <c r="I38" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J38" s="12" t="s">
+      <c r="J38" s="10" t="s">
         <v>2096</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="7">
+      <c r="A39">
         <v>2023</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="7" t="s">
         <v>2104</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>2105</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="14">
         <v>45054</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="14">
         <v>45057</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="7" t="s">
         <v>2094</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="7" t="s">
         <v>2101</v>
       </c>
-      <c r="I39" s="10" t="s">
+      <c r="I39" s="8" t="s">
         <v>2038</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="J39" s="10" t="s">
         <v>2096</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7">
+      <c r="A40">
         <v>2023</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="7" t="s">
         <v>2106</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="7" t="s">
         <v>2107</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E40" s="16">
+      <c r="E40" s="14">
         <v>45054</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="14">
         <v>45057</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="7" t="s">
         <v>2108</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="7" t="s">
         <v>2109</v>
       </c>
-      <c r="I40" s="10" t="s">
+      <c r="I40" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J40" s="12" t="s">
+      <c r="J40" s="10" t="s">
         <v>2110</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="7">
+      <c r="A41">
         <v>2023</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="7" t="s">
         <v>2111</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="7" t="s">
         <v>2112</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E41" s="11" t="s">
+      <c r="E41" s="9" t="s">
         <v>2077</v>
       </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="9" t="s">
         <v>2113</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="7" t="s">
         <v>2108</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="7" t="s">
         <v>2109</v>
       </c>
-      <c r="I41" s="10" t="s">
+      <c r="I41" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J41" s="12" t="s">
+      <c r="J41" s="10" t="s">
         <v>2110</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7">
+      <c r="A42">
         <v>2023</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="7" t="s">
         <v>2114</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="8" t="s">
         <v>2115</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="9" t="s">
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="7" t="s">
         <v>2108</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="7" t="s">
         <v>2109</v>
       </c>
-      <c r="I42" s="10" t="s">
+      <c r="I42" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J42" s="12" t="s">
+      <c r="J42" s="10" t="s">
         <v>2110</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="7">
+      <c r="A43">
         <v>2023</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="7" t="s">
         <v>2116</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="8" t="s">
         <v>2117</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="9">
         <v>44936</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="9">
         <v>44959</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="7" t="s">
         <v>2119</v>
       </c>
-      <c r="I43" s="10" t="s">
+      <c r="I43" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="J43" s="10" t="s">
         <v>2120</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7">
+      <c r="A44">
         <v>2023</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="7" t="s">
         <v>2121</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="8" t="s">
         <v>2122</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="9">
         <v>44936</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="9">
         <v>44959</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="7" t="s">
         <v>2118</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="7" t="s">
         <v>2119</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="I44" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J44" s="12" t="s">
+      <c r="J44" s="10" t="s">
         <v>2120</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="7">
+      <c r="A45">
         <v>2023</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="7" t="s">
         <v>2123</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="8" t="s">
         <v>2124</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="E45" s="9" t="s">
         <v>2125</v>
       </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="9" t="s">
         <v>2126</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="7" t="s">
         <v>2127</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="7" t="s">
         <v>2128</v>
       </c>
-      <c r="I45" s="10" t="s">
+      <c r="I45" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J45" s="12" t="s">
+      <c r="J45" s="10" t="s">
         <v>2129</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7">
+      <c r="A46">
         <v>2023</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="7" t="s">
         <v>2130</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="8" t="s">
         <v>2131</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="9" t="s">
         <v>2132</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="9" t="s">
         <v>2133</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="7" t="s">
         <v>2134</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="7" t="s">
         <v>2135</v>
       </c>
-      <c r="I46" s="10" t="s">
+      <c r="I46" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J46" s="12" t="s">
+      <c r="J46" s="10" t="s">
         <v>2136</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="7">
+      <c r="A47">
         <v>2023</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="7" t="s">
         <v>2137</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="8" t="s">
         <v>1956</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="9" t="s">
         <v>2058</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="9" t="s">
         <v>2059</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="7" t="s">
         <v>2138</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="7" t="s">
         <v>2139</v>
       </c>
-      <c r="I47" s="10" t="s">
+      <c r="I47" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J47" s="12" t="s">
+      <c r="J47" s="10" t="s">
         <v>2140</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7">
+      <c r="A48">
         <v>2023</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="7" t="s">
         <v>2141</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="9" t="s">
         <v>2132</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="9" t="s">
         <v>2133</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="7" t="s">
         <v>2143</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="7" t="s">
         <v>2144</v>
       </c>
-      <c r="I48" s="10" t="s">
+      <c r="I48" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J48" s="12" t="s">
+      <c r="J48" s="10" t="s">
         <v>2140</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="7">
+      <c r="A49">
         <v>2023</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="7" t="s">
         <v>2145</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="8" t="s">
         <v>2146</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="9">
         <v>45054</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="9">
         <v>45057</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="7" t="s">
         <v>2147</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="7" t="s">
         <v>2109</v>
       </c>
-      <c r="I49" s="10" t="s">
+      <c r="I49" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J49" s="12">
+      <c r="J49" s="10">
         <v>45260</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="7">
+      <c r="A50">
         <v>2023</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="7" t="s">
         <v>2148</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="7" t="s">
         <v>2149</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="9" t="s">
         <v>2150</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="9" t="s">
         <v>2151</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="7" t="s">
         <v>2152</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="7" t="s">
         <v>2153</v>
       </c>
-      <c r="I50" s="10" t="s">
+      <c r="I50" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J50" s="12" t="s">
+      <c r="J50" s="10" t="s">
         <v>2154</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="7">
+      <c r="A51">
         <v>2023</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="7" t="s">
         <v>2155</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="8" t="s">
         <v>2156</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="9" t="s">
         <v>1994</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="9" t="s">
         <v>2126</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="7" t="s">
         <v>2157</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="7" t="s">
         <v>2158</v>
       </c>
-      <c r="I51" s="10" t="s">
+      <c r="I51" s="8" t="s">
         <v>1964</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="J51" s="10" t="s">
         <v>2159</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7">
+      <c r="A52">
         <v>2023</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="7" t="s">
         <v>2160</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="7" t="s">
         <v>2161</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="9" t="s">
         <v>2000</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="9" t="s">
         <v>2001</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="7" t="s">
         <v>2162</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="7" t="s">
         <v>2163</v>
       </c>
-      <c r="I52" s="10" t="s">
+      <c r="I52" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="J52" s="10" t="s">
         <v>2164</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="7">
+      <c r="A53">
         <v>2023</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="7" t="s">
         <v>2165</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="8" t="s">
         <v>2166</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="9" t="s">
         <v>2011</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="9" t="s">
         <v>2133</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="7" t="s">
         <v>2162</v>
       </c>
-      <c r="H53" s="9" t="s">
+      <c r="H53" s="7" t="s">
         <v>2163</v>
       </c>
-      <c r="I53" s="10" t="s">
+      <c r="I53" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="J53" s="10" t="s">
         <v>2164</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="7">
+      <c r="A54">
         <v>2023</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="7" t="s">
         <v>2167</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="8" t="s">
         <v>2168</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="9" t="s">
         <v>2055</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="9" t="s">
         <v>2169</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="7" t="s">
         <v>2162</v>
       </c>
-      <c r="H54" s="9" t="s">
+      <c r="H54" s="7" t="s">
         <v>2163</v>
       </c>
-      <c r="I54" s="10" t="s">
+      <c r="I54" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J54" s="12" t="s">
+      <c r="J54" s="10" t="s">
         <v>2164</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="7">
+      <c r="A55">
         <v>2023</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="11" t="s">
         <v>2170</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="8" t="s">
         <v>2171</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="9" t="s">
         <v>2172</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="9">
         <v>45047</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="7" t="s">
         <v>2173</v>
       </c>
-      <c r="H55" s="9" t="s">
+      <c r="H55" s="7" t="s">
         <v>2128</v>
       </c>
-      <c r="I55" s="10" t="s">
+      <c r="I55" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J55" s="12" t="s">
+      <c r="J55" s="10" t="s">
         <v>2174</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="7">
+      <c r="A56">
         <v>2023</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="7" t="s">
         <v>2175</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="8" t="s">
         <v>1951</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="9" t="s">
         <v>2176</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="9">
         <v>45200</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="7" t="s">
         <v>2173</v>
       </c>
-      <c r="H56" s="9" t="s">
+      <c r="H56" s="7" t="s">
         <v>2128</v>
       </c>
-      <c r="I56" s="10" t="s">
+      <c r="I56" s="8" t="s">
         <v>1954</v>
       </c>
-      <c r="J56" s="12" t="s">
+      <c r="J56" s="10" t="s">
         <v>2174</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="7">
+      <c r="A57">
         <v>2022</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="7" t="s">
         <v>2177</v>
       </c>
-      <c r="C57" s="10" t="s">
+      <c r="C57" s="8" t="s">
         <v>2178</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E57" s="18">
+      <c r="E57" s="16">
         <v>44207</v>
       </c>
-      <c r="F57" s="19">
+      <c r="F57" s="17">
         <v>44684</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="G57" s="18" t="s">
         <v>2179</v>
       </c>
-      <c r="H57" s="20" t="s">
+      <c r="H57" s="18" t="s">
         <v>2180</v>
       </c>
-      <c r="I57" s="20" t="s">
+      <c r="I57" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J57" s="21" t="s">
+      <c r="J57" s="19" t="s">
         <v>2181</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
+      <c r="A58">
         <v>2022</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="7" t="s">
         <v>2182</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="8" t="s">
         <v>2183</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E58" s="18">
+      <c r="E58" s="16">
         <v>44327</v>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="17">
         <v>44684</v>
       </c>
-      <c r="G58" s="20" t="s">
+      <c r="G58" s="18" t="s">
         <v>2179</v>
       </c>
-      <c r="H58" s="20" t="s">
+      <c r="H58" s="18" t="s">
         <v>2180</v>
       </c>
-      <c r="I58" s="20" t="s">
+      <c r="I58" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J58" s="21" t="s">
+      <c r="J58" s="19" t="s">
         <v>2181</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="7">
+      <c r="A59">
         <v>2022</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>2184</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="8" t="s">
         <v>2185</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E59" s="18">
+      <c r="E59" s="16">
         <v>44207</v>
       </c>
-      <c r="F59" s="19">
+      <c r="F59" s="17">
         <v>44684</v>
       </c>
-      <c r="G59" s="20" t="s">
+      <c r="G59" s="18" t="s">
         <v>2179</v>
       </c>
-      <c r="H59" s="20" t="s">
+      <c r="H59" s="18" t="s">
         <v>2180</v>
       </c>
-      <c r="I59" s="20" t="s">
+      <c r="I59" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J59" s="21" t="s">
+      <c r="J59" s="19" t="s">
         <v>2181</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="7">
+      <c r="A60">
         <v>2022</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="7" t="s">
         <v>2186</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="8" t="s">
         <v>2187</v>
       </c>
-      <c r="D60" s="17" t="s">
+      <c r="D60" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E60" s="18">
+      <c r="E60" s="16">
         <v>44326</v>
       </c>
-      <c r="F60" s="19">
+      <c r="F60" s="17">
         <v>44684</v>
       </c>
-      <c r="G60" s="20" t="s">
+      <c r="G60" s="18" t="s">
         <v>2188</v>
       </c>
-      <c r="H60" s="20" t="s">
+      <c r="H60" s="18" t="s">
         <v>2189</v>
       </c>
-      <c r="I60" s="20" t="s">
+      <c r="I60" s="18" t="s">
         <v>1964</v>
       </c>
-      <c r="J60" s="21" t="s">
+      <c r="J60" s="19" t="s">
         <v>2190</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="7">
+      <c r="A61">
         <v>2022</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="7" t="s">
         <v>2191</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="8" t="s">
         <v>2192</v>
       </c>
-      <c r="D61" s="17" t="s">
+      <c r="D61" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="16" t="s">
         <v>2193</v>
       </c>
-      <c r="F61" s="19" t="s">
+      <c r="F61" s="17" t="s">
         <v>2194</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="G61" s="18" t="s">
         <v>2195</v>
       </c>
-      <c r="H61" s="20" t="s">
+      <c r="H61" s="18" t="s">
         <v>2196</v>
       </c>
-      <c r="I61" s="20" t="s">
+      <c r="I61" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J61" s="21" t="s">
+      <c r="J61" s="19" t="s">
         <v>2197</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="7">
+      <c r="A62">
         <v>2022</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="7" t="s">
         <v>2198</v>
       </c>
-      <c r="C62" s="10" t="s">
+      <c r="C62" s="8" t="s">
         <v>2199</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="16" t="s">
         <v>2200</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="17" t="s">
         <v>2201</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="G62" s="18" t="s">
         <v>2202</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="18" t="s">
         <v>2203</v>
       </c>
-      <c r="I62" s="20" t="s">
+      <c r="I62" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J62" s="21" t="s">
+      <c r="J62" s="19" t="s">
         <v>2204</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
+      <c r="A63">
         <v>2022</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="7" t="s">
         <v>2205</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C63" s="8" t="s">
         <v>2206</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E63" s="18" t="s">
+      <c r="E63" s="16" t="s">
         <v>2207</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="17" t="s">
         <v>2208</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="G63" s="18" t="s">
         <v>2209</v>
       </c>
-      <c r="H63" s="20" t="s">
+      <c r="H63" s="18" t="s">
         <v>2210</v>
       </c>
-      <c r="I63" s="20" t="s">
+      <c r="I63" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J63" s="21" t="s">
+      <c r="J63" s="19" t="s">
         <v>2211</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="7">
+      <c r="A64">
         <v>2022</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="7" t="s">
         <v>2212</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="7" t="s">
         <v>2213</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="16">
         <v>44836</v>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="17">
         <v>44839</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="G64" s="18" t="s">
         <v>2214</v>
       </c>
-      <c r="H64" s="20" t="s">
+      <c r="H64" s="18" t="s">
         <v>2215</v>
       </c>
-      <c r="I64" s="20" t="s">
+      <c r="I64" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J64" s="21" t="s">
+      <c r="J64" s="19" t="s">
         <v>2216</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
+      <c r="A65">
         <v>2022</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="7" t="s">
         <v>2217</v>
       </c>
-      <c r="C65" s="9" t="s">
+      <c r="C65" s="7" t="s">
         <v>2218</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E65" s="18">
+      <c r="E65" s="16">
         <v>44682</v>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="17">
         <v>44686</v>
       </c>
-      <c r="G65" s="20" t="s">
+      <c r="G65" s="18" t="s">
         <v>2219</v>
       </c>
-      <c r="H65" s="20" t="s">
+      <c r="H65" s="18" t="s">
         <v>2220</v>
       </c>
-      <c r="I65" s="20" t="s">
+      <c r="I65" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J65" s="21" t="s">
+      <c r="J65" s="19" t="s">
         <v>2221</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="7">
+      <c r="A66">
         <v>2022</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="7" t="s">
         <v>2222</v>
       </c>
-      <c r="C66" s="10" t="s">
+      <c r="C66" s="8" t="s">
         <v>2223</v>
       </c>
-      <c r="D66" s="17" t="s">
+      <c r="D66" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E66" s="18">
+      <c r="E66" s="16">
         <v>44682</v>
       </c>
-      <c r="F66" s="19">
+      <c r="F66" s="17">
         <v>44686</v>
       </c>
-      <c r="G66" s="20" t="s">
+      <c r="G66" s="18" t="s">
         <v>2219</v>
       </c>
-      <c r="H66" s="20" t="s">
+      <c r="H66" s="18" t="s">
         <v>2220</v>
       </c>
-      <c r="I66" s="20" t="s">
+      <c r="I66" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J66" s="21" t="s">
+      <c r="J66" s="19" t="s">
         <v>2221</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
+      <c r="A67">
         <v>2022</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="7" t="s">
         <v>2224</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="7" t="s">
         <v>2225</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E67" s="18" t="s">
+      <c r="E67" s="16" t="s">
         <v>2226</v>
       </c>
-      <c r="F67" s="19" t="s">
+      <c r="F67" s="17" t="s">
         <v>2022</v>
       </c>
-      <c r="G67" s="20" t="s">
+      <c r="G67" s="18" t="s">
         <v>2227</v>
       </c>
-      <c r="H67" s="20" t="s">
+      <c r="H67" s="18" t="s">
         <v>2227</v>
       </c>
-      <c r="I67" s="20" t="s">
+      <c r="I67" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J67" s="21" t="s">
+      <c r="J67" s="19" t="s">
         <v>2228</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="7">
+      <c r="A68">
         <v>2022</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="7" t="s">
         <v>2229</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="7" t="s">
         <v>2230</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E68" s="18">
+      <c r="E68" s="16">
         <v>44835</v>
       </c>
-      <c r="F68" s="19">
+      <c r="F68" s="17">
         <v>44840</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="G68" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H68" s="20" t="s">
+      <c r="H68" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I68" s="20" t="s">
+      <c r="I68" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J68" s="21" t="s">
+      <c r="J68" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
+      <c r="A69">
         <v>2022</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="7" t="s">
         <v>2233</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="8" t="s">
         <v>2234</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E69" s="18">
+      <c r="E69" s="16">
         <v>44682</v>
       </c>
-      <c r="F69" s="19">
+      <c r="F69" s="17">
         <v>44686</v>
       </c>
-      <c r="G69" s="20" t="s">
+      <c r="G69" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H69" s="20" t="s">
+      <c r="H69" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I69" s="20" t="s">
+      <c r="I69" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J69" s="21" t="s">
+      <c r="J69" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="7">
+      <c r="A70">
         <v>2022</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="7" t="s">
         <v>2235</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="7" t="s">
         <v>2236</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E70" s="18" t="s">
+      <c r="E70" s="16" t="s">
         <v>2237</v>
       </c>
-      <c r="F70" s="19" t="s">
+      <c r="F70" s="17" t="s">
         <v>2238</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="G70" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H70" s="20" t="s">
+      <c r="H70" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I70" s="20" t="s">
+      <c r="I70" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J70" s="21" t="s">
+      <c r="J70" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="7">
+      <c r="A71">
         <v>2022</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="7" t="s">
         <v>2239</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="8" t="s">
         <v>2131</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E71" s="18">
+      <c r="E71" s="16">
         <v>44835</v>
       </c>
-      <c r="F71" s="19">
+      <c r="F71" s="17">
         <v>44840</v>
       </c>
-      <c r="G71" s="20" t="s">
+      <c r="G71" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H71" s="20" t="s">
+      <c r="H71" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I71" s="20" t="s">
+      <c r="I71" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J71" s="21" t="s">
+      <c r="J71" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="7">
+      <c r="A72">
         <v>2022</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="7" t="s">
         <v>2240</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="7" t="s">
         <v>2241</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="16">
         <v>44835</v>
       </c>
-      <c r="F72" s="19">
+      <c r="F72" s="17">
         <v>44840</v>
       </c>
-      <c r="G72" s="20" t="s">
+      <c r="G72" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H72" s="20" t="s">
+      <c r="H72" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I72" s="20" t="s">
+      <c r="I72" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J72" s="21" t="s">
+      <c r="J72" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="7">
+      <c r="A73">
         <v>2022</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="7" t="s">
         <v>2242</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="7" t="s">
         <v>2243</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="16" t="s">
         <v>2237</v>
       </c>
-      <c r="F73" s="19" t="s">
+      <c r="F73" s="17" t="s">
         <v>2244</v>
       </c>
-      <c r="G73" s="20" t="s">
+      <c r="G73" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H73" s="20" t="s">
+      <c r="H73" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I73" s="20" t="s">
+      <c r="I73" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J73" s="21" t="s">
+      <c r="J73" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="7">
+      <c r="A74">
         <v>2022</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="7" t="s">
         <v>2245</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="7" t="s">
         <v>2246</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E74" s="18">
+      <c r="E74" s="16">
         <v>44682</v>
       </c>
-      <c r="F74" s="19">
+      <c r="F74" s="17">
         <v>44686</v>
       </c>
-      <c r="G74" s="20" t="s">
+      <c r="G74" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H74" s="20" t="s">
+      <c r="H74" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I74" s="20" t="s">
+      <c r="I74" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J74" s="21" t="s">
+      <c r="J74" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="7">
+      <c r="A75">
         <v>2022</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="7" t="s">
         <v>2247</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="7" t="s">
         <v>2248</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E75" s="18" t="s">
+      <c r="E75" s="16" t="s">
         <v>2237</v>
       </c>
-      <c r="F75" s="19" t="s">
+      <c r="F75" s="17" t="s">
         <v>2238</v>
       </c>
-      <c r="G75" s="20" t="s">
+      <c r="G75" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H75" s="20" t="s">
+      <c r="H75" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I75" s="20" t="s">
+      <c r="I75" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J75" s="21" t="s">
+      <c r="J75" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="7">
+      <c r="A76">
         <v>2022</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="7" t="s">
         <v>2249</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="7" t="s">
         <v>2250</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E76" s="18">
+      <c r="E76" s="16">
         <v>44563</v>
       </c>
-      <c r="F76" s="19">
+      <c r="F76" s="17">
         <v>44567</v>
       </c>
-      <c r="G76" s="20" t="s">
+      <c r="G76" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H76" s="20" t="s">
+      <c r="H76" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I76" s="20" t="s">
+      <c r="I76" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J76" s="21" t="s">
+      <c r="J76" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="7">
+      <c r="A77">
         <v>2022</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="7" t="s">
         <v>2251</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="7" t="s">
         <v>2252</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E77" s="18">
+      <c r="E77" s="16">
         <v>44682</v>
       </c>
-      <c r="F77" s="19">
+      <c r="F77" s="17">
         <v>44686</v>
       </c>
-      <c r="G77" s="20" t="s">
+      <c r="G77" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H77" s="20" t="s">
+      <c r="H77" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I77" s="20" t="s">
+      <c r="I77" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J77" s="21" t="s">
+      <c r="J77" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="7">
+      <c r="A78">
         <v>2022</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="7" t="s">
         <v>2253</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="7" t="s">
         <v>2254</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E78" s="18">
+      <c r="E78" s="16">
         <v>44563</v>
       </c>
-      <c r="F78" s="19">
+      <c r="F78" s="17">
         <v>44567</v>
       </c>
-      <c r="G78" s="20" t="s">
+      <c r="G78" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H78" s="20" t="s">
+      <c r="H78" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I78" s="20" t="s">
+      <c r="I78" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J78" s="21" t="s">
+      <c r="J78" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
+      <c r="A79">
         <v>2022</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="7" t="s">
         <v>2255</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="7" t="s">
         <v>2256</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E79" s="18">
+      <c r="E79" s="16">
         <v>44563</v>
       </c>
-      <c r="F79" s="19">
+      <c r="F79" s="17">
         <v>44567</v>
       </c>
-      <c r="G79" s="20" t="s">
+      <c r="G79" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H79" s="20" t="s">
+      <c r="H79" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I79" s="20" t="s">
+      <c r="I79" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J79" s="21" t="s">
+      <c r="J79" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="7">
+      <c r="A80">
         <v>2022</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="7" t="s">
         <v>2257</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="8" t="s">
         <v>2258</v>
       </c>
-      <c r="D80" s="17" t="s">
+      <c r="D80" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E80" s="18" t="s">
+      <c r="E80" s="16" t="s">
         <v>2259</v>
       </c>
-      <c r="F80" s="19" t="s">
+      <c r="F80" s="17" t="s">
         <v>2260</v>
       </c>
-      <c r="G80" s="20" t="s">
+      <c r="G80" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H80" s="20" t="s">
+      <c r="H80" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I80" s="20" t="s">
+      <c r="I80" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J80" s="21" t="s">
+      <c r="J80" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7">
+      <c r="A81">
         <v>2022</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="7" t="s">
         <v>2261</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="7" t="s">
         <v>2262</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E81" s="18">
+      <c r="E81" s="16">
         <v>44682</v>
       </c>
-      <c r="F81" s="19">
+      <c r="F81" s="17">
         <v>44686</v>
       </c>
-      <c r="G81" s="20" t="s">
+      <c r="G81" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H81" s="20" t="s">
+      <c r="H81" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I81" s="20" t="s">
+      <c r="I81" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J81" s="21" t="s">
+      <c r="J81" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="7">
+      <c r="A82">
         <v>2022</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="7" t="s">
         <v>2263</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="7" t="s">
         <v>2264</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E82" s="18">
+      <c r="E82" s="16">
         <v>44563</v>
       </c>
-      <c r="F82" s="19">
+      <c r="F82" s="17">
         <v>44567</v>
       </c>
-      <c r="G82" s="20" t="s">
+      <c r="G82" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H82" s="20" t="s">
+      <c r="H82" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I82" s="20" t="s">
+      <c r="I82" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J82" s="21" t="s">
+      <c r="J82" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7">
+      <c r="A83">
         <v>2022</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="7" t="s">
         <v>2265</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="8" t="s">
         <v>2266</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="16" t="s">
         <v>2259</v>
       </c>
-      <c r="F83" s="19" t="s">
+      <c r="F83" s="17" t="s">
         <v>2260</v>
       </c>
-      <c r="G83" s="20" t="s">
+      <c r="G83" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H83" s="20" t="s">
+      <c r="H83" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I83" s="20" t="s">
+      <c r="I83" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J83" s="21" t="s">
+      <c r="J83" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="7">
+      <c r="A84">
         <v>2022</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="7" t="s">
         <v>2267</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="8" t="s">
         <v>2268</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E84" s="18">
+      <c r="E84" s="16">
         <v>44682</v>
       </c>
-      <c r="F84" s="19">
+      <c r="F84" s="17">
         <v>44686</v>
       </c>
-      <c r="G84" s="20" t="s">
+      <c r="G84" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H84" s="20" t="s">
+      <c r="H84" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I84" s="20" t="s">
+      <c r="I84" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J84" s="21" t="s">
+      <c r="J84" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="7">
+      <c r="A85">
         <v>2022</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="7" t="s">
         <v>2269</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="8" t="s">
         <v>2270</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E85" s="18">
+      <c r="E85" s="16">
         <v>44682</v>
       </c>
-      <c r="F85" s="19">
+      <c r="F85" s="17">
         <v>44686</v>
       </c>
-      <c r="G85" s="20" t="s">
+      <c r="G85" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H85" s="20" t="s">
+      <c r="H85" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I85" s="20" t="s">
+      <c r="I85" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J85" s="21" t="s">
+      <c r="J85" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="7">
+      <c r="A86">
         <v>2022</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="7" t="s">
         <v>2271</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" s="7" t="s">
         <v>2272</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E86" s="18">
+      <c r="E86" s="16">
         <v>44682</v>
       </c>
-      <c r="F86" s="19">
+      <c r="F86" s="17">
         <v>44686</v>
       </c>
-      <c r="G86" s="20" t="s">
+      <c r="G86" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H86" s="20" t="s">
+      <c r="H86" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I86" s="20" t="s">
+      <c r="I86" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J86" s="21" t="s">
+      <c r="J86" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="7">
+      <c r="A87">
         <v>2022</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="7" t="s">
         <v>2273</v>
       </c>
-      <c r="C87" s="10" t="s">
+      <c r="C87" s="8" t="s">
         <v>2274</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E87" s="18">
+      <c r="E87" s="16">
         <v>44682</v>
       </c>
-      <c r="F87" s="19">
+      <c r="F87" s="17">
         <v>44686</v>
       </c>
-      <c r="G87" s="20" t="s">
+      <c r="G87" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H87" s="20" t="s">
+      <c r="H87" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I87" s="20" t="s">
+      <c r="I87" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J87" s="21" t="s">
+      <c r="J87" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="7">
+      <c r="A88">
         <v>2022</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="7" t="s">
         <v>2275</v>
       </c>
-      <c r="C88" s="10" t="s">
+      <c r="C88" s="8" t="s">
         <v>2276</v>
       </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E88" s="18">
+      <c r="E88" s="16">
         <v>44563</v>
       </c>
-      <c r="F88" s="19">
+      <c r="F88" s="17">
         <v>44567</v>
       </c>
-      <c r="G88" s="20" t="s">
+      <c r="G88" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H88" s="20" t="s">
+      <c r="H88" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I88" s="20" t="s">
+      <c r="I88" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J88" s="21" t="s">
+      <c r="J88" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="89" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="7">
+      <c r="A89">
         <v>2022</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="7" t="s">
         <v>2277</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="7" t="s">
         <v>2278</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E89" s="18">
+      <c r="E89" s="16">
         <v>44682</v>
       </c>
-      <c r="F89" s="19">
+      <c r="F89" s="17">
         <v>44686</v>
       </c>
-      <c r="G89" s="20" t="s">
+      <c r="G89" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H89" s="20" t="s">
+      <c r="H89" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I89" s="20" t="s">
+      <c r="I89" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J89" s="21" t="s">
+      <c r="J89" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7">
+      <c r="A90">
         <v>2022</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="7" t="s">
         <v>2279</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="7" t="s">
         <v>2280</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E90" s="18">
+      <c r="E90" s="16">
         <v>44682</v>
       </c>
-      <c r="F90" s="19">
+      <c r="F90" s="17">
         <v>44686</v>
       </c>
-      <c r="G90" s="20" t="s">
+      <c r="G90" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H90" s="20" t="s">
+      <c r="H90" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I90" s="20" t="s">
+      <c r="I90" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J90" s="21" t="s">
+      <c r="J90" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="7">
+      <c r="A91">
         <v>2022</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="7" t="s">
         <v>2281</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" s="8" t="s">
         <v>2282</v>
       </c>
-      <c r="D91" s="17" t="s">
+      <c r="D91" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E91" s="18">
+      <c r="E91" s="16">
         <v>44682</v>
       </c>
-      <c r="F91" s="19">
+      <c r="F91" s="17">
         <v>44686</v>
       </c>
-      <c r="G91" s="20" t="s">
+      <c r="G91" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H91" s="20" t="s">
+      <c r="H91" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I91" s="20" t="s">
+      <c r="I91" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J91" s="21" t="s">
+      <c r="J91" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="7">
+      <c r="A92">
         <v>2022</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="7" t="s">
         <v>2283</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="8" t="s">
         <v>2284</v>
       </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E92" s="18">
+      <c r="E92" s="16">
         <v>44682</v>
       </c>
-      <c r="F92" s="19">
+      <c r="F92" s="17">
         <v>44686</v>
       </c>
-      <c r="G92" s="20" t="s">
+      <c r="G92" s="18" t="s">
         <v>2231</v>
       </c>
-      <c r="H92" s="20" t="s">
+      <c r="H92" s="18" t="s">
         <v>2232</v>
       </c>
-      <c r="I92" s="20" t="s">
+      <c r="I92" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J92" s="21" t="s">
+      <c r="J92" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="7">
+      <c r="A93">
         <v>2022</v>
       </c>
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="7" t="s">
         <v>2285</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E93" s="18" t="s">
+      <c r="E93" s="16" t="s">
         <v>2286</v>
       </c>
-      <c r="F93" s="19" t="s">
+      <c r="F93" s="17" t="s">
         <v>2287</v>
       </c>
-      <c r="G93" s="20" t="s">
+      <c r="G93" s="18" t="s">
         <v>2288</v>
       </c>
-      <c r="H93" s="20" t="s">
+      <c r="H93" s="18" t="s">
         <v>2289</v>
       </c>
-      <c r="I93" s="20" t="s">
+      <c r="I93" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J93" s="21" t="s">
+      <c r="J93" s="19" t="s">
         <v>2290</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="7">
+      <c r="A94">
         <v>2022</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="7" t="s">
         <v>2291</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C94" s="7" t="s">
         <v>2292</v>
       </c>
-      <c r="D94" s="17" t="s">
+      <c r="D94" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E94" s="18">
+      <c r="E94" s="16">
         <v>44564</v>
       </c>
-      <c r="F94" s="19">
+      <c r="F94" s="17">
         <v>44570</v>
       </c>
-      <c r="G94" s="20" t="s">
+      <c r="G94" s="18" t="s">
         <v>2293</v>
       </c>
-      <c r="H94" s="20" t="s">
+      <c r="H94" s="18" t="s">
         <v>2294</v>
       </c>
-      <c r="I94" s="20" t="s">
+      <c r="I94" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J94" s="21" t="s">
+      <c r="J94" s="19" t="s">
         <v>2295</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="7">
+      <c r="A95">
         <v>2022</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="7" t="s">
         <v>2296</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C95" s="7" t="s">
         <v>2297</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D95" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E95" s="18" t="s">
+      <c r="E95" s="16" t="s">
         <v>2298</v>
       </c>
-      <c r="F95" s="19" t="s">
+      <c r="F95" s="17" t="s">
         <v>2299</v>
       </c>
-      <c r="G95" s="20" t="s">
+      <c r="G95" s="18" t="s">
         <v>2300</v>
       </c>
-      <c r="H95" s="20" t="s">
+      <c r="H95" s="18" t="s">
         <v>2301</v>
       </c>
-      <c r="I95" s="20" t="s">
+      <c r="I95" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J95" s="21" t="s">
+      <c r="J95" s="19" t="s">
         <v>2302</v>
       </c>
     </row>
     <row r="96" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="7">
+      <c r="A96">
         <v>2022</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="7" t="s">
         <v>2303</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="7" t="s">
         <v>2304</v>
       </c>
-      <c r="D96" s="17" t="s">
+      <c r="D96" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E96" s="18">
+      <c r="E96" s="16">
         <v>44568</v>
       </c>
-      <c r="F96" s="19">
+      <c r="F96" s="17">
         <v>44571</v>
       </c>
-      <c r="G96" s="20" t="s">
+      <c r="G96" s="18" t="s">
         <v>2305</v>
       </c>
-      <c r="H96" s="20" t="s">
+      <c r="H96" s="18" t="s">
         <v>2306</v>
       </c>
-      <c r="I96" s="20" t="s">
+      <c r="I96" s="18" t="s">
         <v>1964</v>
       </c>
-      <c r="J96" s="21" t="s">
+      <c r="J96" s="19" t="s">
         <v>2307</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="7">
+      <c r="A97">
         <v>2022</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="7" t="s">
         <v>2308</v>
       </c>
-      <c r="C97" s="9" t="s">
+      <c r="C97" s="7" t="s">
         <v>2309</v>
       </c>
-      <c r="D97" s="17" t="s">
+      <c r="D97" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E97" s="18" t="s">
+      <c r="E97" s="16" t="s">
         <v>2310</v>
       </c>
-      <c r="F97" s="19" t="s">
+      <c r="F97" s="17" t="s">
         <v>2299</v>
       </c>
-      <c r="G97" s="20" t="s">
+      <c r="G97" s="18" t="s">
         <v>2305</v>
       </c>
-      <c r="H97" s="20" t="s">
+      <c r="H97" s="18" t="s">
         <v>2306</v>
       </c>
-      <c r="I97" s="20" t="s">
+      <c r="I97" s="18" t="s">
         <v>1964</v>
       </c>
-      <c r="J97" s="21" t="s">
+      <c r="J97" s="19" t="s">
         <v>2307</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="7">
+      <c r="A98">
         <v>2022</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="7" t="s">
         <v>2311</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C98" s="8" t="s">
         <v>2312</v>
       </c>
-      <c r="D98" s="17" t="s">
+      <c r="D98" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E98" s="18" t="s">
+      <c r="E98" s="16" t="s">
         <v>2313</v>
       </c>
-      <c r="F98" s="19" t="s">
+      <c r="F98" s="17" t="s">
         <v>2314</v>
       </c>
-      <c r="G98" s="20" t="s">
+      <c r="G98" s="18" t="s">
         <v>2315</v>
       </c>
-      <c r="H98" s="20" t="s">
+      <c r="H98" s="18" t="s">
         <v>2316</v>
       </c>
-      <c r="I98" s="20" t="s">
+      <c r="I98" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J98" s="21" t="s">
+      <c r="J98" s="19" t="s">
         <v>2317</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="7">
+      <c r="A99">
         <v>2022</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="7" t="s">
         <v>2318</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C99" s="8" t="s">
         <v>2319</v>
       </c>
-      <c r="D99" s="17" t="s">
+      <c r="D99" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E99" s="18">
+      <c r="E99" s="16">
         <v>44566</v>
       </c>
-      <c r="F99" s="19">
+      <c r="F99" s="17">
         <v>44572</v>
       </c>
-      <c r="G99" s="20" t="s">
+      <c r="G99" s="18" t="s">
         <v>2320</v>
       </c>
-      <c r="H99" s="20" t="s">
+      <c r="H99" s="18" t="s">
         <v>2144</v>
       </c>
-      <c r="I99" s="20" t="s">
+      <c r="I99" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J99" s="21" t="s">
+      <c r="J99" s="19" t="s">
         <v>2321</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="7">
+      <c r="A100">
         <v>2022</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="7" t="s">
         <v>2322</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E100" s="18">
+      <c r="E100" s="16">
         <v>44568</v>
       </c>
-      <c r="F100" s="19">
+      <c r="F100" s="17">
         <v>44573</v>
       </c>
-      <c r="G100" s="20" t="s">
+      <c r="G100" s="18" t="s">
         <v>2320</v>
       </c>
-      <c r="H100" s="20" t="s">
+      <c r="H100" s="18" t="s">
         <v>2144</v>
       </c>
-      <c r="I100" s="20" t="s">
+      <c r="I100" s="18" t="s">
         <v>1954</v>
       </c>
-      <c r="J100" s="21" t="s">
+      <c r="J100" s="19" t="s">
         <v>2321</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="7">
+      <c r="A101">
         <v>2022</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="7" t="s">
         <v>2323</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C101" s="8" t="s">
         <v>2324</v>
       </c>
-      <c r="D101" s="17" t="s">
+      <c r="D101" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E101" s="18" t="s">
+      <c r="E101" s="16" t="s">
         <v>2298</v>
       </c>
-      <c r="F101" s="19" t="s">
+      <c r="F101" s="17" t="s">
         <v>2314</v>
       </c>
-      <c r="G101" s="20" t="s">
+      <c r="G101" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H101" s="20" t="s">
+      <c r="H101" s="18" t="s">
         <v>2326</v>
       </c>
-      <c r="I101" s="20" t="s">
+      <c r="I101" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J101" s="21" t="s">
+      <c r="J101" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="7">
+      <c r="A102">
         <v>2022</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="7" t="s">
         <v>2328</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="7" t="s">
         <v>2329</v>
       </c>
-      <c r="D102" s="17" t="s">
+      <c r="D102" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E102" s="18" t="s">
+      <c r="E102" s="16" t="s">
         <v>2287</v>
       </c>
-      <c r="F102" s="19" t="s">
+      <c r="F102" s="17" t="s">
         <v>2010</v>
       </c>
-      <c r="G102" s="20" t="s">
+      <c r="G102" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H102" s="20" t="s">
+      <c r="H102" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I102" s="20" t="s">
+      <c r="I102" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J102" s="21" t="s">
+      <c r="J102" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="7">
+      <c r="A103">
         <v>2022</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="7" t="s">
         <v>2331</v>
       </c>
-      <c r="C103" s="9" t="s">
+      <c r="C103" s="7" t="s">
         <v>2332</v>
       </c>
-      <c r="D103" s="17" t="s">
+      <c r="D103" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E103" s="18" t="s">
+      <c r="E103" s="16" t="s">
         <v>2298</v>
       </c>
-      <c r="F103" s="19" t="s">
+      <c r="F103" s="17" t="s">
         <v>2010</v>
       </c>
-      <c r="G103" s="20" t="s">
+      <c r="G103" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H103" s="20" t="s">
+      <c r="H103" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I103" s="20" t="s">
+      <c r="I103" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J103" s="21" t="s">
+      <c r="J103" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="7">
+      <c r="A104">
         <v>2022</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="7" t="s">
         <v>2333</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C104" s="8" t="s">
         <v>2067</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="D104" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E104" s="18" t="s">
+      <c r="E104" s="16" t="s">
         <v>2022</v>
       </c>
-      <c r="F104" s="19" t="s">
+      <c r="F104" s="17" t="s">
         <v>2334</v>
       </c>
-      <c r="G104" s="20" t="s">
+      <c r="G104" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H104" s="20" t="s">
+      <c r="H104" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I104" s="20" t="s">
+      <c r="I104" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J104" s="21" t="s">
+      <c r="J104" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="7">
+      <c r="A105">
         <v>2022</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="7" t="s">
         <v>2335</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C105" s="8" t="s">
         <v>2336</v>
       </c>
-      <c r="D105" s="17" t="s">
+      <c r="D105" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E105" s="18">
+      <c r="E105" s="16">
         <v>44567</v>
       </c>
-      <c r="F105" s="19">
+      <c r="F105" s="17">
         <v>44573</v>
       </c>
-      <c r="G105" s="20" t="s">
+      <c r="G105" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H105" s="20" t="s">
+      <c r="H105" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I105" s="20" t="s">
+      <c r="I105" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J105" s="21" t="s">
+      <c r="J105" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="106" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="7">
+      <c r="A106">
         <v>2022</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" s="7" t="s">
         <v>2337</v>
       </c>
-      <c r="C106" s="9" t="s">
+      <c r="C106" s="7" t="s">
         <v>2338</v>
       </c>
-      <c r="D106" s="17" t="s">
+      <c r="D106" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E106" s="18">
+      <c r="E106" s="16">
         <v>44207</v>
       </c>
-      <c r="F106" s="19">
+      <c r="F106" s="17">
         <v>44572</v>
       </c>
-      <c r="G106" s="20" t="s">
+      <c r="G106" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H106" s="20" t="s">
+      <c r="H106" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I106" s="20" t="s">
+      <c r="I106" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J106" s="21" t="s">
+      <c r="J106" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="7">
+      <c r="A107">
         <v>2022</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" s="7" t="s">
         <v>2339</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" s="8" t="s">
         <v>2340</v>
       </c>
-      <c r="D107" s="17" t="s">
+      <c r="D107" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E107" s="18">
+      <c r="E107" s="16">
         <v>44565</v>
       </c>
-      <c r="F107" s="22">
+      <c r="F107" s="20">
         <v>44568</v>
       </c>
-      <c r="G107" s="20" t="s">
+      <c r="G107" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H107" s="20" t="s">
+      <c r="H107" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I107" s="20" t="s">
+      <c r="I107" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J107" s="21" t="s">
+      <c r="J107" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="108" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="7">
+      <c r="A108">
         <v>2022</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" s="7" t="s">
         <v>2341</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="8" t="s">
         <v>2342</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E108" s="18">
+      <c r="E108" s="16">
         <v>44564</v>
       </c>
-      <c r="F108" s="22">
+      <c r="F108" s="20">
         <v>44568</v>
       </c>
-      <c r="G108" s="20" t="s">
+      <c r="G108" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H108" s="20" t="s">
+      <c r="H108" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I108" s="20" t="s">
+      <c r="I108" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J108" s="21" t="s">
+      <c r="J108" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="109" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="7">
+      <c r="A109">
         <v>2022</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" s="7" t="s">
         <v>2343</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C109" s="8" t="s">
         <v>2344</v>
       </c>
-      <c r="D109" s="17" t="s">
+      <c r="D109" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E109" s="18" t="s">
+      <c r="E109" s="16" t="s">
         <v>2286</v>
       </c>
-      <c r="F109" s="22" t="s">
+      <c r="F109" s="20" t="s">
         <v>2314</v>
       </c>
-      <c r="G109" s="20" t="s">
+      <c r="G109" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H109" s="20" t="s">
+      <c r="H109" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I109" s="20" t="s">
+      <c r="I109" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J109" s="21" t="s">
+      <c r="J109" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="110" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="7">
+      <c r="A110">
         <v>2022</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" s="7" t="s">
         <v>2345</v>
       </c>
-      <c r="C110" s="10" t="s">
+      <c r="C110" s="8" t="s">
         <v>2346</v>
       </c>
-      <c r="D110" s="17" t="s">
+      <c r="D110" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E110" s="18">
+      <c r="E110" s="16">
         <v>44564</v>
       </c>
-      <c r="F110" s="22">
+      <c r="F110" s="20">
         <v>44570</v>
       </c>
-      <c r="G110" s="20" t="s">
+      <c r="G110" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H110" s="20" t="s">
+      <c r="H110" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I110" s="20" t="s">
+      <c r="I110" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J110" s="21" t="s">
+      <c r="J110" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="111" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="7">
+      <c r="A111">
         <v>2022</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" s="7" t="s">
         <v>2347</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="7" t="s">
         <v>2348</v>
       </c>
-      <c r="D111" s="17" t="s">
+      <c r="D111" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E111" s="18">
+      <c r="E111" s="16">
         <v>44565</v>
       </c>
-      <c r="F111" s="22">
+      <c r="F111" s="20">
         <v>44569</v>
       </c>
-      <c r="G111" s="20" t="s">
+      <c r="G111" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H111" s="20" t="s">
+      <c r="H111" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I111" s="20" t="s">
+      <c r="I111" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J111" s="21" t="s">
+      <c r="J111" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="112" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="7">
+      <c r="A112">
         <v>2022</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" s="7" t="s">
         <v>2343</v>
       </c>
-      <c r="C112" s="10" t="s">
+      <c r="C112" s="8" t="s">
         <v>2349</v>
       </c>
-      <c r="D112" s="17" t="s">
+      <c r="D112" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E112" s="18" t="s">
+      <c r="E112" s="16" t="s">
         <v>2287</v>
       </c>
-      <c r="F112" s="19" t="s">
+      <c r="F112" s="17" t="s">
         <v>2010</v>
       </c>
-      <c r="G112" s="20" t="s">
+      <c r="G112" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H112" s="20" t="s">
+      <c r="H112" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I112" s="20" t="s">
+      <c r="I112" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J112" s="21" t="s">
+      <c r="J112" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="7">
+      <c r="A113">
         <v>2022</v>
       </c>
-      <c r="B113" s="9" t="s">
+      <c r="B113" s="7" t="s">
         <v>2350</v>
       </c>
-      <c r="C113" s="10" t="s">
+      <c r="C113" s="8" t="s">
         <v>2351</v>
       </c>
-      <c r="D113" s="17" t="s">
+      <c r="D113" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E113" s="18" t="s">
+      <c r="E113" s="16" t="s">
         <v>2352</v>
       </c>
-      <c r="F113" s="19" t="s">
+      <c r="F113" s="17" t="s">
         <v>2022</v>
       </c>
-      <c r="G113" s="20" t="s">
+      <c r="G113" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H113" s="20" t="s">
+      <c r="H113" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I113" s="20" t="s">
+      <c r="I113" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J113" s="21" t="s">
+      <c r="J113" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="114" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="7">
+      <c r="A114">
         <v>2022</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="7" t="s">
         <v>2353</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="7" t="s">
         <v>2354</v>
       </c>
-      <c r="D114" s="17" t="s">
+      <c r="D114" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E114" s="18" t="s">
+      <c r="E114" s="16" t="s">
         <v>2226</v>
       </c>
-      <c r="F114" s="19" t="s">
+      <c r="F114" s="17" t="s">
         <v>2010</v>
       </c>
-      <c r="G114" s="20" t="s">
+      <c r="G114" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H114" s="20" t="s">
+      <c r="H114" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I114" s="20" t="s">
+      <c r="I114" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J114" s="21" t="s">
+      <c r="J114" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="7">
+      <c r="A115">
         <v>2022</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B115" s="7" t="s">
         <v>2355</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="11" t="s">
         <v>2356</v>
       </c>
-      <c r="D115" s="17" t="s">
+      <c r="D115" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E115" s="18">
+      <c r="E115" s="16">
         <v>44564</v>
       </c>
-      <c r="F115" s="19">
+      <c r="F115" s="17">
         <v>44569</v>
       </c>
-      <c r="G115" s="20" t="s">
+      <c r="G115" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H115" s="20" t="s">
+      <c r="H115" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I115" s="20" t="s">
+      <c r="I115" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J115" s="21" t="s">
+      <c r="J115" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="7">
+      <c r="A116">
         <v>2022</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" s="7" t="s">
         <v>2357</v>
       </c>
-      <c r="C116" s="9" t="s">
+      <c r="C116" s="7" t="s">
         <v>2358</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="D116" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E116" s="18">
+      <c r="E116" s="16">
         <v>44565</v>
       </c>
-      <c r="F116" s="19">
+      <c r="F116" s="17">
         <v>44568</v>
       </c>
-      <c r="G116" s="20" t="s">
+      <c r="G116" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H116" s="20" t="s">
+      <c r="H116" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I116" s="20" t="s">
+      <c r="I116" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J116" s="21" t="s">
+      <c r="J116" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="7">
+      <c r="A117">
         <v>2022</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="7" t="s">
         <v>2359</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C117" s="8" t="s">
         <v>2192</v>
       </c>
-      <c r="D117" s="17" t="s">
+      <c r="D117" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E117" s="18">
+      <c r="E117" s="16">
         <v>44566</v>
       </c>
-      <c r="F117" s="19">
+      <c r="F117" s="17">
         <v>44572</v>
       </c>
-      <c r="G117" s="20" t="s">
+      <c r="G117" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H117" s="20" t="s">
+      <c r="H117" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I117" s="20" t="s">
+      <c r="I117" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J117" s="21" t="s">
+      <c r="J117" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="7">
+      <c r="A118">
         <v>2022</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" s="7" t="s">
         <v>2360</v>
       </c>
-      <c r="C118" s="9" t="s">
+      <c r="C118" s="7" t="s">
         <v>2361</v>
       </c>
-      <c r="D118" s="17" t="s">
+      <c r="D118" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E118" s="18" t="s">
+      <c r="E118" s="16" t="s">
         <v>2362</v>
       </c>
-      <c r="F118" s="19" t="s">
+      <c r="F118" s="17" t="s">
         <v>2363</v>
       </c>
-      <c r="G118" s="20" t="s">
+      <c r="G118" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H118" s="20" t="s">
+      <c r="H118" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I118" s="20" t="s">
+      <c r="I118" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J118" s="21" t="s">
+      <c r="J118" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="7">
+      <c r="A119">
         <v>2022</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="7" t="s">
         <v>2364</v>
       </c>
-      <c r="C119" s="9" t="s">
+      <c r="C119" s="7" t="s">
         <v>2365</v>
       </c>
-      <c r="D119" s="17" t="s">
+      <c r="D119" s="15" t="s">
         <v>1951</v>
       </c>
-      <c r="E119" s="18">
+      <c r="E119" s="16">
         <v>44689</v>
       </c>
-      <c r="F119" s="19">
+      <c r="F119" s="17">
         <v>44693</v>
       </c>
-      <c r="G119" s="20" t="s">
+      <c r="G119" s="18" t="s">
         <v>2325</v>
       </c>
-      <c r="H119" s="20" t="s">
+      <c r="H119" s="18" t="s">
         <v>2330</v>
       </c>
-      <c r="I119" s="20" t="s">
+      <c r="I119" s="18" t="s">
         <v>2038</v>
       </c>
-      <c r="J119" s="21" t="s">
+      <c r="J119" s="19" t="s">
         <v>2327</v>
       </c>
     </row>
     <row r="120" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="7">
+      <c r="A120">
         <v>2021</v>
       </c>
-      <c r="B120" s="20" t="s">
+      <c r="B120" s="18" t="s">
         <v>2366</v>
       </c>
-      <c r="C120" s="10" t="s">
+      <c r="C120" s="8" t="s">
         <v>2367</v>
       </c>
-      <c r="D120" s="23" t="s">
+      <c r="D120" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E120" s="18">
+      <c r="E120" s="16">
         <v>44109</v>
       </c>
-      <c r="F120" s="19">
+      <c r="F120" s="17">
         <v>44201</v>
       </c>
-      <c r="G120" s="9" t="s">
+      <c r="G120" s="7" t="s">
         <v>2368</v>
       </c>
-      <c r="H120" s="9" t="s">
+      <c r="H120" s="7" t="s">
         <v>2369</v>
       </c>
-      <c r="I120" s="9" t="s">
+      <c r="I120" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J120" s="24" t="s">
+      <c r="J120" s="22" t="s">
         <v>2370</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="7">
+      <c r="A121">
         <v>2021</v>
       </c>
-      <c r="B121" s="20" t="s">
+      <c r="B121" s="18" t="s">
         <v>2371</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C121" s="8" t="s">
         <v>2372</v>
       </c>
-      <c r="D121" s="23" t="s">
+      <c r="D121" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E121" s="18">
+      <c r="E121" s="16">
         <v>44089</v>
       </c>
-      <c r="F121" s="19">
+      <c r="F121" s="17">
         <v>44545</v>
       </c>
-      <c r="G121" s="9" t="s">
+      <c r="G121" s="7" t="s">
         <v>2368</v>
       </c>
-      <c r="H121" s="9" t="s">
+      <c r="H121" s="7" t="s">
         <v>2369</v>
       </c>
-      <c r="I121" s="9" t="s">
+      <c r="I121" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J121" s="24" t="s">
+      <c r="J121" s="22" t="s">
         <v>2370</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="7">
+      <c r="A122">
         <v>2021</v>
       </c>
-      <c r="B122" s="20" t="s">
+      <c r="B122" s="18" t="s">
         <v>2373</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C122" s="8" t="s">
         <v>2374</v>
       </c>
-      <c r="D122" s="23" t="s">
+      <c r="D122" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E122" s="18">
+      <c r="E122" s="16">
         <v>44109</v>
       </c>
-      <c r="F122" s="19">
+      <c r="F122" s="17">
         <v>44201</v>
       </c>
-      <c r="G122" s="9" t="s">
+      <c r="G122" s="7" t="s">
         <v>2368</v>
       </c>
-      <c r="H122" s="9" t="s">
+      <c r="H122" s="7" t="s">
         <v>2369</v>
       </c>
-      <c r="I122" s="9" t="s">
+      <c r="I122" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J122" s="24" t="s">
+      <c r="J122" s="22" t="s">
         <v>2370</v>
       </c>
     </row>
     <row r="123" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="7">
+      <c r="A123">
         <v>2021</v>
       </c>
-      <c r="B123" s="20" t="s">
+      <c r="B123" s="18" t="s">
         <v>2375</v>
       </c>
-      <c r="C123" s="10" t="s">
+      <c r="C123" s="8" t="s">
         <v>2376</v>
       </c>
-      <c r="D123" s="23" t="s">
+      <c r="D123" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E123" s="18">
+      <c r="E123" s="16">
         <v>44075</v>
       </c>
-      <c r="F123" s="19">
+      <c r="F123" s="17">
         <v>44197</v>
       </c>
-      <c r="G123" s="9" t="s">
+      <c r="G123" s="7" t="s">
         <v>2368</v>
       </c>
-      <c r="H123" s="9" t="s">
+      <c r="H123" s="7" t="s">
         <v>2369</v>
       </c>
-      <c r="I123" s="9" t="s">
+      <c r="I123" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J123" s="24" t="s">
+      <c r="J123" s="22" t="s">
         <v>2370</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="7">
+      <c r="A124">
         <v>2021</v>
       </c>
-      <c r="B124" s="20" t="s">
+      <c r="B124" s="18" t="s">
         <v>2377</v>
       </c>
-      <c r="C124" s="10" t="s">
+      <c r="C124" s="8" t="s">
         <v>2378</v>
       </c>
-      <c r="D124" s="23" t="s">
+      <c r="D124" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E124" s="18">
+      <c r="E124" s="16">
         <v>44089</v>
       </c>
-      <c r="F124" s="19">
+      <c r="F124" s="17">
         <v>44211</v>
       </c>
-      <c r="G124" s="9" t="s">
+      <c r="G124" s="7" t="s">
         <v>2379</v>
       </c>
-      <c r="H124" s="9" t="s">
+      <c r="H124" s="7" t="s">
         <v>2380</v>
       </c>
-      <c r="I124" s="9" t="s">
+      <c r="I124" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J124" s="24" t="s">
+      <c r="J124" s="22" t="s">
         <v>2381</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="7">
+      <c r="A125">
         <v>2021</v>
       </c>
-      <c r="B125" s="20" t="s">
+      <c r="B125" s="18" t="s">
         <v>2382</v>
       </c>
-      <c r="C125" s="10" t="s">
+      <c r="C125" s="8" t="s">
         <v>2383</v>
       </c>
-      <c r="D125" s="23" t="s">
+      <c r="D125" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E125" s="18">
+      <c r="E125" s="16">
         <v>44027</v>
       </c>
-      <c r="F125" s="19">
+      <c r="F125" s="17">
         <v>44180</v>
       </c>
-      <c r="G125" s="9" t="s">
+      <c r="G125" s="7" t="s">
         <v>2379</v>
       </c>
-      <c r="H125" s="9" t="s">
+      <c r="H125" s="7" t="s">
         <v>2380</v>
       </c>
-      <c r="I125" s="9" t="s">
+      <c r="I125" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J125" s="24" t="s">
+      <c r="J125" s="22" t="s">
         <v>2381</v>
       </c>
     </row>
     <row r="126" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="7">
+      <c r="A126">
         <v>2021</v>
       </c>
-      <c r="B126" s="20" t="s">
+      <c r="B126" s="18" t="s">
         <v>2384</v>
       </c>
-      <c r="C126" s="10" t="s">
+      <c r="C126" s="8" t="s">
         <v>2385</v>
       </c>
-      <c r="D126" s="23" t="s">
+      <c r="D126" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E126" s="18">
+      <c r="E126" s="16">
         <v>44089</v>
       </c>
-      <c r="F126" s="19">
+      <c r="F126" s="17">
         <v>44545</v>
       </c>
-      <c r="G126" s="9" t="s">
+      <c r="G126" s="7" t="s">
         <v>2386</v>
       </c>
-      <c r="H126" s="9" t="s">
+      <c r="H126" s="7" t="s">
         <v>2387</v>
       </c>
-      <c r="I126" s="9" t="s">
+      <c r="I126" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J126" s="24" t="s">
+      <c r="J126" s="22" t="s">
         <v>2388</v>
       </c>
     </row>
     <row r="127" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="7">
+      <c r="A127">
         <v>2021</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" s="11" t="s">
         <v>2389</v>
       </c>
-      <c r="C127" s="10" t="s">
+      <c r="C127" s="8" t="s">
         <v>2185</v>
       </c>
-      <c r="D127" s="23" t="s">
+      <c r="D127" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E127" s="18">
+      <c r="E127" s="16">
         <v>44166</v>
       </c>
-      <c r="F127" s="19">
+      <c r="F127" s="17">
         <v>44228</v>
       </c>
-      <c r="G127" s="9" t="s">
+      <c r="G127" s="7" t="s">
         <v>2386</v>
       </c>
-      <c r="H127" s="9" t="s">
+      <c r="H127" s="7" t="s">
         <v>2387</v>
       </c>
-      <c r="I127" s="9" t="s">
+      <c r="I127" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J127" s="24" t="s">
+      <c r="J127" s="22" t="s">
         <v>2388</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="7">
+      <c r="A128">
         <v>2021</v>
       </c>
-      <c r="B128" s="13" t="s">
+      <c r="B128" s="11" t="s">
         <v>2390</v>
       </c>
-      <c r="C128" s="10" t="s">
+      <c r="C128" s="8" t="s">
         <v>2178</v>
       </c>
-      <c r="D128" s="23" t="s">
+      <c r="D128" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E128" s="18">
+      <c r="E128" s="16">
         <v>43845</v>
       </c>
-      <c r="F128" s="19">
+      <c r="F128" s="17">
         <v>43997</v>
       </c>
-      <c r="G128" s="9" t="s">
+      <c r="G128" s="7" t="s">
         <v>2386</v>
       </c>
-      <c r="H128" s="9" t="s">
+      <c r="H128" s="7" t="s">
         <v>2387</v>
       </c>
-      <c r="I128" s="9" t="s">
+      <c r="I128" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J128" s="24" t="s">
+      <c r="J128" s="22" t="s">
         <v>2388</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="7">
+      <c r="A129">
         <v>2021</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="11" t="s">
         <v>2391</v>
       </c>
-      <c r="C129" s="10" t="s">
+      <c r="C129" s="8" t="s">
         <v>2376</v>
       </c>
-      <c r="D129" s="23" t="s">
+      <c r="D129" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E129" s="18">
+      <c r="E129" s="16">
         <v>44105</v>
       </c>
-      <c r="F129" s="19">
+      <c r="F129" s="17">
         <v>44211</v>
       </c>
-      <c r="G129" s="9" t="s">
+      <c r="G129" s="7" t="s">
         <v>2386</v>
       </c>
-      <c r="H129" s="9" t="s">
+      <c r="H129" s="7" t="s">
         <v>2387</v>
       </c>
-      <c r="I129" s="9" t="s">
+      <c r="I129" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J129" s="24" t="s">
+      <c r="J129" s="22" t="s">
         <v>2388</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="7">
+      <c r="A130">
         <v>2021</v>
       </c>
-      <c r="B130" s="13" t="s">
+      <c r="B130" s="11" t="s">
         <v>2392</v>
       </c>
-      <c r="C130" s="10" t="s">
+      <c r="C130" s="8" t="s">
         <v>2393</v>
       </c>
-      <c r="D130" s="23" t="s">
+      <c r="D130" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E130" s="18">
+      <c r="E130" s="16">
         <v>44119</v>
       </c>
-      <c r="F130" s="19">
+      <c r="F130" s="17">
         <v>44242</v>
       </c>
-      <c r="G130" s="9" t="s">
+      <c r="G130" s="7" t="s">
         <v>2386</v>
       </c>
-      <c r="H130" s="9" t="s">
+      <c r="H130" s="7" t="s">
         <v>2387</v>
       </c>
-      <c r="I130" s="9" t="s">
+      <c r="I130" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J130" s="24" t="s">
+      <c r="J130" s="22" t="s">
         <v>2388</v>
       </c>
     </row>
     <row r="131" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="7">
+      <c r="A131">
         <v>2021</v>
       </c>
-      <c r="B131" s="13" t="s">
+      <c r="B131" s="11" t="s">
         <v>2394</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="7" t="s">
         <v>2395</v>
       </c>
-      <c r="D131" s="25" t="s">
+      <c r="D131" s="23" t="s">
         <v>2396</v>
       </c>
-      <c r="E131" s="18">
+      <c r="E131" s="16">
         <v>43831</v>
       </c>
-      <c r="F131" s="19">
+      <c r="F131" s="17">
         <v>44926</v>
       </c>
-      <c r="G131" s="9" t="s">
+      <c r="G131" s="7" t="s">
         <v>2397</v>
       </c>
-      <c r="H131" s="9" t="s">
+      <c r="H131" s="7" t="s">
         <v>2398</v>
       </c>
-      <c r="I131" s="9" t="s">
+      <c r="I131" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J131" s="24" t="s">
+      <c r="J131" s="22" t="s">
         <v>2399</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="7">
+      <c r="A132">
         <v>2021</v>
       </c>
-      <c r="B132" s="13" t="s">
+      <c r="B132" s="11" t="s">
         <v>2400</v>
       </c>
-      <c r="C132" s="10" t="s">
+      <c r="C132" s="8" t="s">
         <v>2401</v>
       </c>
-      <c r="D132" s="23" t="s">
+      <c r="D132" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E132" s="18">
+      <c r="E132" s="16">
         <v>44180</v>
       </c>
-      <c r="F132" s="19">
+      <c r="F132" s="17">
         <v>44270</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="G132" s="7" t="s">
         <v>2402</v>
       </c>
-      <c r="H132" s="9" t="s">
+      <c r="H132" s="7" t="s">
         <v>2403</v>
       </c>
-      <c r="I132" s="9" t="s">
+      <c r="I132" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J132" s="24" t="s">
+      <c r="J132" s="22" t="s">
         <v>2404</v>
       </c>
     </row>
     <row r="133" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="7">
+      <c r="A133">
         <v>2021</v>
       </c>
-      <c r="B133" s="13" t="s">
+      <c r="B133" s="11" t="s">
         <v>2405</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C133" s="8" t="s">
         <v>2372</v>
       </c>
-      <c r="D133" s="23" t="s">
+      <c r="D133" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E133" s="18">
+      <c r="E133" s="16">
         <v>44206</v>
       </c>
-      <c r="F133" s="19">
+      <c r="F133" s="17">
         <v>44265</v>
       </c>
-      <c r="G133" s="9" t="s">
+      <c r="G133" s="7" t="s">
         <v>2406</v>
       </c>
-      <c r="H133" s="9" t="s">
+      <c r="H133" s="7" t="s">
         <v>2407</v>
       </c>
-      <c r="I133" s="9" t="s">
+      <c r="I133" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J133" s="24" t="s">
+      <c r="J133" s="22" t="s">
         <v>2408</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="7">
+      <c r="A134">
         <v>2021</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="11" t="s">
         <v>2409</v>
       </c>
-      <c r="C134" s="10" t="s">
+      <c r="C134" s="8" t="s">
         <v>2087</v>
       </c>
-      <c r="D134" s="23" t="s">
+      <c r="D134" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E134" s="18">
+      <c r="E134" s="16">
         <v>44201</v>
       </c>
-      <c r="F134" s="19">
+      <c r="F134" s="17">
         <v>44291</v>
       </c>
-      <c r="G134" s="9" t="s">
+      <c r="G134" s="7" t="s">
         <v>2410</v>
       </c>
-      <c r="H134" s="9" t="s">
+      <c r="H134" s="7" t="s">
         <v>2411</v>
       </c>
-      <c r="I134" s="9" t="s">
+      <c r="I134" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J134" s="24" t="s">
+      <c r="J134" s="22" t="s">
         <v>2412</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="7">
+      <c r="A135">
         <v>2021</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="11" t="s">
         <v>2413</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" s="7" t="s">
         <v>2414</v>
       </c>
-      <c r="D135" s="23" t="s">
+      <c r="D135" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E135" s="18">
+      <c r="E135" s="16">
         <v>44180</v>
       </c>
-      <c r="F135" s="19">
+      <c r="F135" s="17">
         <v>44301</v>
       </c>
-      <c r="G135" s="9" t="s">
+      <c r="G135" s="7" t="s">
         <v>2415</v>
       </c>
-      <c r="H135" s="9" t="s">
+      <c r="H135" s="7" t="s">
         <v>2416</v>
       </c>
-      <c r="I135" s="9" t="s">
+      <c r="I135" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J135" s="24" t="s">
+      <c r="J135" s="22" t="s">
         <v>2417</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="7">
+      <c r="A136">
         <v>2021</v>
       </c>
-      <c r="B136" s="13" t="s">
+      <c r="B136" s="11" t="s">
         <v>2418</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C136" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="D136" s="23" t="s">
+      <c r="D136" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E136" s="18">
+      <c r="E136" s="16">
         <v>44150</v>
       </c>
-      <c r="F136" s="19">
+      <c r="F136" s="17">
         <v>44301</v>
       </c>
-      <c r="G136" s="9" t="s">
+      <c r="G136" s="7" t="s">
         <v>2420</v>
       </c>
-      <c r="H136" s="9" t="s">
+      <c r="H136" s="7" t="s">
         <v>2421</v>
       </c>
-      <c r="I136" s="9" t="s">
+      <c r="I136" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J136" s="24" t="s">
+      <c r="J136" s="22" t="s">
         <v>2422</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="7">
+      <c r="A137">
         <v>2021</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="11" t="s">
         <v>2423</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C137" s="8" t="s">
         <v>2424</v>
       </c>
-      <c r="D137" s="23" t="s">
+      <c r="D137" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E137" s="18">
+      <c r="E137" s="16">
         <v>43845</v>
       </c>
-      <c r="F137" s="19">
+      <c r="F137" s="17">
         <v>43997</v>
       </c>
-      <c r="G137" s="9" t="s">
+      <c r="G137" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H137" s="9" t="s">
+      <c r="H137" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I137" s="9" t="s">
+      <c r="I137" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J137" s="24">
+      <c r="J137" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="7">
+      <c r="A138">
         <v>2021</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" s="11" t="s">
         <v>2427</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="7" t="s">
         <v>2428</v>
       </c>
-      <c r="D138" s="23" t="s">
+      <c r="D138" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E138" s="18">
+      <c r="E138" s="16">
         <v>44211</v>
       </c>
-      <c r="F138" s="19">
+      <c r="F138" s="17">
         <v>44331</v>
       </c>
-      <c r="G138" s="9" t="s">
+      <c r="G138" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H138" s="9" t="s">
+      <c r="H138" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I138" s="9" t="s">
+      <c r="I138" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J138" s="24">
+      <c r="J138" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="7">
+      <c r="A139">
         <v>2021</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" s="11" t="s">
         <v>2429</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="7" t="s">
         <v>2430</v>
       </c>
-      <c r="D139" s="23" t="s">
+      <c r="D139" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E139" s="18">
+      <c r="E139" s="16">
         <v>44211</v>
       </c>
-      <c r="F139" s="19">
+      <c r="F139" s="17">
         <v>44331</v>
       </c>
-      <c r="G139" s="9" t="s">
+      <c r="G139" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H139" s="9" t="s">
+      <c r="H139" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I139" s="9" t="s">
+      <c r="I139" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J139" s="24">
+      <c r="J139" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="140" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="7">
+      <c r="A140">
         <v>2021</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" s="11" t="s">
         <v>2431</v>
       </c>
-      <c r="C140" s="10" t="s">
+      <c r="C140" s="8" t="s">
         <v>2432</v>
       </c>
-      <c r="D140" s="23" t="s">
+      <c r="D140" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E140" s="18">
+      <c r="E140" s="16">
         <v>44256</v>
       </c>
-      <c r="F140" s="19">
+      <c r="F140" s="17">
         <v>44348</v>
       </c>
-      <c r="G140" s="9" t="s">
+      <c r="G140" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H140" s="9" t="s">
+      <c r="H140" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I140" s="9" t="s">
+      <c r="I140" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J140" s="24">
+      <c r="J140" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="7">
+      <c r="A141">
         <v>2021</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" s="11" t="s">
         <v>2433</v>
       </c>
-      <c r="C141" s="10" t="s">
+      <c r="C141" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="D141" s="23" t="s">
+      <c r="D141" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E141" s="18">
+      <c r="E141" s="16">
         <v>44180</v>
       </c>
-      <c r="F141" s="19">
+      <c r="F141" s="17">
         <v>44362</v>
       </c>
-      <c r="G141" s="9" t="s">
+      <c r="G141" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H141" s="9" t="s">
+      <c r="H141" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I141" s="9" t="s">
+      <c r="I141" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J141" s="24">
+      <c r="J141" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="7">
+      <c r="A142">
         <v>2021</v>
       </c>
-      <c r="B142" s="26" t="s">
+      <c r="B142" s="24" t="s">
         <v>2434</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="7" t="s">
         <v>2435</v>
       </c>
-      <c r="D142" s="25" t="s">
+      <c r="D142" s="23" t="s">
         <v>2396</v>
       </c>
-      <c r="E142" s="18">
+      <c r="E142" s="16">
         <v>2017</v>
       </c>
-      <c r="F142" s="19">
+      <c r="F142" s="17">
         <v>2021</v>
       </c>
-      <c r="G142" s="9" t="s">
+      <c r="G142" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H142" s="9" t="s">
+      <c r="H142" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I142" s="9" t="s">
+      <c r="I142" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J142" s="24">
+      <c r="J142" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="143" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="7">
+      <c r="A143">
         <v>2021</v>
       </c>
-      <c r="B143" s="26" t="s">
+      <c r="B143" s="24" t="s">
         <v>2436</v>
       </c>
-      <c r="C143" s="10" t="s">
+      <c r="C143" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="D143" s="23" t="s">
+      <c r="D143" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E143" s="18">
+      <c r="E143" s="16">
         <v>44211</v>
       </c>
-      <c r="F143" s="19">
+      <c r="F143" s="17">
         <v>44362</v>
       </c>
-      <c r="G143" s="9" t="s">
+      <c r="G143" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H143" s="9" t="s">
+      <c r="H143" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I143" s="9" t="s">
+      <c r="I143" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J143" s="24">
+      <c r="J143" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="144" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="7">
+      <c r="A144">
         <v>2021</v>
       </c>
-      <c r="B144" s="26" t="s">
+      <c r="B144" s="24" t="s">
         <v>2438</v>
       </c>
-      <c r="C144" s="10" t="s">
+      <c r="C144" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="D144" s="23" t="s">
+      <c r="D144" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E144" s="18">
+      <c r="E144" s="16">
         <v>44216</v>
       </c>
-      <c r="F144" s="19">
+      <c r="F144" s="17">
         <v>44336</v>
       </c>
-      <c r="G144" s="9" t="s">
+      <c r="G144" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H144" s="9" t="s">
+      <c r="H144" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I144" s="9" t="s">
+      <c r="I144" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J144" s="24">
+      <c r="J144" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="145" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="7">
+      <c r="A145">
         <v>2021</v>
       </c>
-      <c r="B145" s="26" t="s">
+      <c r="B145" s="24" t="s">
         <v>2440</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="7" t="s">
         <v>2441</v>
       </c>
-      <c r="D145" s="23" t="s">
+      <c r="D145" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E145" s="18">
+      <c r="E145" s="16">
         <v>44211</v>
       </c>
-      <c r="F145" s="19">
+      <c r="F145" s="17">
         <v>44331</v>
       </c>
-      <c r="G145" s="9" t="s">
+      <c r="G145" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H145" s="9" t="s">
+      <c r="H145" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I145" s="9" t="s">
+      <c r="I145" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J145" s="24">
+      <c r="J145" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="146" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="7">
+      <c r="A146">
         <v>2021</v>
       </c>
-      <c r="B146" s="26" t="s">
+      <c r="B146" s="24" t="s">
         <v>2442</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="7" t="s">
         <v>2443</v>
       </c>
-      <c r="D146" s="23" t="s">
+      <c r="D146" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E146" s="18">
+      <c r="E146" s="16">
         <v>44211</v>
       </c>
-      <c r="F146" s="19">
+      <c r="F146" s="17">
         <v>44362</v>
       </c>
-      <c r="G146" s="9" t="s">
+      <c r="G146" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H146" s="9" t="s">
+      <c r="H146" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I146" s="9" t="s">
+      <c r="I146" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J146" s="24">
+      <c r="J146" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="147" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="7">
+      <c r="A147">
         <v>2021</v>
       </c>
-      <c r="B147" s="26" t="s">
+      <c r="B147" s="24" t="s">
         <v>2444</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="7" t="s">
         <v>2445</v>
       </c>
-      <c r="D147" s="23" t="s">
+      <c r="D147" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E147" s="18">
+      <c r="E147" s="16">
         <v>44180</v>
       </c>
-      <c r="F147" s="19">
+      <c r="F147" s="17">
         <v>44362</v>
       </c>
-      <c r="G147" s="9" t="s">
+      <c r="G147" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H147" s="9" t="s">
+      <c r="H147" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I147" s="9" t="s">
+      <c r="I147" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J147" s="24">
+      <c r="J147" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="148" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="7">
+      <c r="A148">
         <v>2021</v>
       </c>
-      <c r="B148" s="26" t="s">
+      <c r="B148" s="24" t="s">
         <v>2446</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="7" t="s">
         <v>2447</v>
       </c>
-      <c r="D148" s="23" t="s">
+      <c r="D148" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E148" s="18">
+      <c r="E148" s="16">
         <v>44216</v>
       </c>
-      <c r="F148" s="19">
+      <c r="F148" s="17">
         <v>44336</v>
       </c>
-      <c r="G148" s="9" t="s">
+      <c r="G148" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H148" s="9" t="s">
+      <c r="H148" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I148" s="9" t="s">
+      <c r="I148" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J148" s="24">
+      <c r="J148" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="149" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="7">
+      <c r="A149">
         <v>2021</v>
       </c>
-      <c r="B149" s="26" t="s">
+      <c r="B149" s="24" t="s">
         <v>2446</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="7" t="s">
         <v>2448</v>
       </c>
-      <c r="D149" s="23" t="s">
+      <c r="D149" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E149" s="18">
+      <c r="E149" s="16">
         <v>44153</v>
       </c>
-      <c r="F149" s="19">
+      <c r="F149" s="17">
         <v>44273</v>
       </c>
-      <c r="G149" s="9" t="s">
+      <c r="G149" s="7" t="s">
         <v>2425</v>
       </c>
-      <c r="H149" s="9" t="s">
+      <c r="H149" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I149" s="9" t="s">
+      <c r="I149" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J149" s="24">
+      <c r="J149" s="22">
         <v>44376</v>
       </c>
     </row>
     <row r="150" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="7">
+      <c r="A150">
         <v>2021</v>
       </c>
-      <c r="B150" s="26" t="s">
+      <c r="B150" s="24" t="s">
         <v>2449</v>
       </c>
-      <c r="C150" s="10" t="s">
+      <c r="C150" s="8" t="s">
         <v>2450</v>
       </c>
-      <c r="D150" s="23" t="s">
+      <c r="D150" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E150" s="18">
+      <c r="E150" s="16">
         <v>44211</v>
       </c>
-      <c r="F150" s="19">
+      <c r="F150" s="17">
         <v>44362</v>
       </c>
-      <c r="G150" s="9" t="s">
+      <c r="G150" s="7" t="s">
         <v>2451</v>
       </c>
-      <c r="H150" s="9" t="s">
+      <c r="H150" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I150" s="9" t="s">
+      <c r="I150" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J150" s="24" t="s">
+      <c r="J150" s="22" t="s">
         <v>2452</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="7">
+      <c r="A151">
         <v>2021</v>
       </c>
-      <c r="B151" s="26" t="s">
+      <c r="B151" s="24" t="s">
         <v>2453</v>
       </c>
-      <c r="C151" s="10" t="s">
+      <c r="C151" s="8" t="s">
         <v>2454</v>
       </c>
-      <c r="D151" s="23" t="s">
+      <c r="D151" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E151" s="18">
+      <c r="E151" s="16">
         <v>44211</v>
       </c>
-      <c r="F151" s="19">
+      <c r="F151" s="17">
         <v>44362</v>
       </c>
-      <c r="G151" s="9" t="s">
+      <c r="G151" s="7" t="s">
         <v>2451</v>
       </c>
-      <c r="H151" s="9" t="s">
+      <c r="H151" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I151" s="9" t="s">
+      <c r="I151" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J151" s="24" t="s">
+      <c r="J151" s="22" t="s">
         <v>2452</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="7">
+      <c r="A152">
         <v>2021</v>
       </c>
-      <c r="B152" s="26" t="s">
+      <c r="B152" s="24" t="s">
         <v>2455</v>
       </c>
-      <c r="C152" s="10" t="s">
+      <c r="C152" s="8" t="s">
         <v>2456</v>
       </c>
-      <c r="D152" s="23" t="s">
+      <c r="D152" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E152" s="18">
+      <c r="E152" s="16">
         <v>44211</v>
       </c>
-      <c r="F152" s="19">
+      <c r="F152" s="17">
         <v>44362</v>
       </c>
-      <c r="G152" s="9" t="s">
+      <c r="G152" s="7" t="s">
         <v>2451</v>
       </c>
-      <c r="H152" s="9" t="s">
+      <c r="H152" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I152" s="9" t="s">
+      <c r="I152" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J152" s="24" t="s">
+      <c r="J152" s="22" t="s">
         <v>2452</v>
       </c>
     </row>
     <row r="153" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="7">
+      <c r="A153">
         <v>2021</v>
       </c>
-      <c r="B153" s="26" t="s">
+      <c r="B153" s="24" t="s">
         <v>2457</v>
       </c>
-      <c r="C153" s="10" t="s">
+      <c r="C153" s="8" t="s">
         <v>2458</v>
       </c>
-      <c r="D153" s="23" t="s">
+      <c r="D153" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E153" s="18">
+      <c r="E153" s="16">
         <v>44201</v>
       </c>
-      <c r="F153" s="19">
+      <c r="F153" s="17">
         <v>44321</v>
       </c>
-      <c r="G153" s="9" t="s">
+      <c r="G153" s="7" t="s">
         <v>2451</v>
       </c>
-      <c r="H153" s="9" t="s">
+      <c r="H153" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I153" s="9" t="s">
+      <c r="I153" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J153" s="24" t="s">
+      <c r="J153" s="22" t="s">
         <v>2452</v>
       </c>
     </row>
     <row r="154" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="7">
+      <c r="A154">
         <v>2021</v>
       </c>
-      <c r="B154" s="26" t="s">
+      <c r="B154" s="24" t="s">
         <v>2459</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C154" s="8" t="s">
         <v>2460</v>
       </c>
-      <c r="D154" s="23" t="s">
+      <c r="D154" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E154" s="18">
+      <c r="E154" s="16">
         <v>44150</v>
       </c>
-      <c r="F154" s="19">
+      <c r="F154" s="17">
         <v>44301</v>
       </c>
-      <c r="G154" s="9" t="s">
+      <c r="G154" s="7" t="s">
         <v>2461</v>
       </c>
-      <c r="H154" s="9" t="s">
+      <c r="H154" s="7" t="s">
         <v>2462</v>
       </c>
-      <c r="I154" s="9" t="s">
+      <c r="I154" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J154" s="24" t="s">
+      <c r="J154" s="22" t="s">
         <v>2463</v>
       </c>
     </row>
     <row r="155" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="7">
+      <c r="A155">
         <v>2021</v>
       </c>
-      <c r="B155" s="26" t="s">
+      <c r="B155" s="24" t="s">
         <v>2464</v>
       </c>
-      <c r="C155" s="10" t="s">
+      <c r="C155" s="8" t="s">
         <v>2142</v>
       </c>
-      <c r="D155" s="23" t="s">
+      <c r="D155" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E155" s="18">
+      <c r="E155" s="16">
         <v>44216</v>
       </c>
-      <c r="F155" s="19">
+      <c r="F155" s="17">
         <v>44367</v>
       </c>
-      <c r="G155" s="9" t="s">
+      <c r="G155" s="7" t="s">
         <v>2465</v>
       </c>
-      <c r="H155" s="9" t="s">
+      <c r="H155" s="7" t="s">
         <v>2466</v>
       </c>
-      <c r="I155" s="9" t="s">
+      <c r="I155" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J155" s="24" t="s">
+      <c r="J155" s="22" t="s">
         <v>2467</v>
       </c>
     </row>
     <row r="156" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="7">
+      <c r="A156">
         <v>2021</v>
       </c>
-      <c r="B156" s="26" t="s">
+      <c r="B156" s="24" t="s">
         <v>2468</v>
       </c>
-      <c r="C156" s="9" t="s">
+      <c r="C156" s="7" t="s">
         <v>2469</v>
       </c>
-      <c r="D156" s="23" t="s">
+      <c r="D156" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E156" s="18">
+      <c r="E156" s="16">
         <v>44242</v>
       </c>
-      <c r="F156" s="19">
+      <c r="F156" s="17">
         <v>44392</v>
       </c>
-      <c r="G156" s="9" t="s">
+      <c r="G156" s="7" t="s">
         <v>2470</v>
       </c>
-      <c r="H156" s="9" t="s">
+      <c r="H156" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I156" s="9" t="s">
+      <c r="I156" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J156" s="24" t="s">
+      <c r="J156" s="22" t="s">
         <v>2471</v>
       </c>
     </row>
     <row r="157" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="7">
+      <c r="A157">
         <v>2021</v>
       </c>
-      <c r="B157" s="26" t="s">
+      <c r="B157" s="24" t="s">
         <v>2472</v>
       </c>
-      <c r="C157" s="9" t="s">
+      <c r="C157" s="7" t="s">
         <v>2473</v>
       </c>
-      <c r="D157" s="25" t="s">
+      <c r="D157" s="23" t="s">
         <v>2396</v>
       </c>
-      <c r="E157" s="18">
+      <c r="E157" s="16">
         <v>43831</v>
       </c>
-      <c r="F157" s="19">
+      <c r="F157" s="17">
         <v>44926</v>
       </c>
-      <c r="G157" s="9" t="s">
+      <c r="G157" s="7" t="s">
         <v>2474</v>
       </c>
-      <c r="H157" s="9" t="s">
+      <c r="H157" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I157" s="9" t="s">
+      <c r="I157" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J157" s="24" t="s">
+      <c r="J157" s="22" t="s">
         <v>2475</v>
       </c>
     </row>
     <row r="158" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="7">
+      <c r="A158">
         <v>2021</v>
       </c>
-      <c r="B158" s="26" t="s">
+      <c r="B158" s="24" t="s">
         <v>2476</v>
       </c>
-      <c r="C158" s="10" t="s">
+      <c r="C158" s="8" t="s">
         <v>2477</v>
       </c>
-      <c r="D158" s="23" t="s">
+      <c r="D158" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E158" s="18">
+      <c r="E158" s="16">
         <v>44362</v>
       </c>
-      <c r="F158" s="19">
+      <c r="F158" s="17">
         <v>44484</v>
       </c>
-      <c r="G158" s="9" t="s">
+      <c r="G158" s="7" t="s">
         <v>2478</v>
       </c>
-      <c r="H158" s="9" t="s">
+      <c r="H158" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I158" s="9" t="s">
+      <c r="I158" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J158" s="24" t="s">
+      <c r="J158" s="22" t="s">
         <v>2480</v>
       </c>
     </row>
     <row r="159" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="7">
+      <c r="A159">
         <v>2021</v>
       </c>
-      <c r="B159" s="26" t="s">
+      <c r="B159" s="24" t="s">
         <v>2481</v>
       </c>
-      <c r="C159" s="9" t="s">
+      <c r="C159" s="7" t="s">
         <v>2482</v>
       </c>
-      <c r="D159" s="23" t="s">
+      <c r="D159" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E159" s="18">
+      <c r="E159" s="16">
         <v>44440</v>
       </c>
-      <c r="F159" s="19">
+      <c r="F159" s="17">
         <v>44501</v>
       </c>
-      <c r="G159" s="9" t="s">
+      <c r="G159" s="7" t="s">
         <v>2478</v>
       </c>
-      <c r="H159" s="9" t="s">
+      <c r="H159" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I159" s="9" t="s">
+      <c r="I159" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J159" s="24" t="s">
+      <c r="J159" s="22" t="s">
         <v>2480</v>
       </c>
     </row>
     <row r="160" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="7">
+      <c r="A160">
         <v>2021</v>
       </c>
-      <c r="B160" s="26" t="s">
+      <c r="B160" s="24" t="s">
         <v>2483</v>
       </c>
-      <c r="C160" s="9" t="s">
+      <c r="C160" s="7" t="s">
         <v>2484</v>
       </c>
-      <c r="D160" s="23" t="s">
+      <c r="D160" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E160" s="18">
+      <c r="E160" s="16">
         <v>44211</v>
       </c>
-      <c r="F160" s="19">
+      <c r="F160" s="17">
         <v>44331</v>
       </c>
-      <c r="G160" s="9" t="s">
+      <c r="G160" s="7" t="s">
         <v>2478</v>
       </c>
-      <c r="H160" s="9" t="s">
+      <c r="H160" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I160" s="9" t="s">
+      <c r="I160" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J160" s="24" t="s">
+      <c r="J160" s="22" t="s">
         <v>2480</v>
       </c>
     </row>
     <row r="161" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="7">
+      <c r="A161">
         <v>2021</v>
       </c>
-      <c r="B161" s="26" t="s">
+      <c r="B161" s="24" t="s">
         <v>2485</v>
       </c>
-      <c r="C161" s="9" t="s">
+      <c r="C161" s="7" t="s">
         <v>2486</v>
       </c>
-      <c r="D161" s="23" t="s">
+      <c r="D161" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E161" s="18">
+      <c r="E161" s="16">
         <v>44153</v>
       </c>
-      <c r="F161" s="19">
+      <c r="F161" s="17">
         <v>44273</v>
       </c>
-      <c r="G161" s="9" t="s">
+      <c r="G161" s="7" t="s">
         <v>2478</v>
       </c>
-      <c r="H161" s="9" t="s">
+      <c r="H161" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I161" s="9" t="s">
+      <c r="I161" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J161" s="24" t="s">
+      <c r="J161" s="22" t="s">
         <v>2480</v>
       </c>
     </row>
     <row r="162" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="7">
+      <c r="A162">
         <v>2021</v>
       </c>
-      <c r="B162" s="26" t="s">
+      <c r="B162" s="24" t="s">
         <v>2487</v>
       </c>
-      <c r="C162" s="10" t="s">
+      <c r="C162" s="8" t="s">
         <v>2258</v>
       </c>
-      <c r="D162" s="23" t="s">
+      <c r="D162" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E162" s="18">
+      <c r="E162" s="16">
         <v>44275</v>
       </c>
-      <c r="F162" s="19">
+      <c r="F162" s="17">
         <v>44428</v>
       </c>
-      <c r="G162" s="9" t="s">
+      <c r="G162" s="7" t="s">
         <v>2488</v>
       </c>
-      <c r="H162" s="9" t="s">
+      <c r="H162" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I162" s="9" t="s">
+      <c r="I162" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J162" s="24" t="s">
+      <c r="J162" s="22" t="s">
         <v>2489</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="7">
+      <c r="A163">
         <v>2021</v>
       </c>
-      <c r="B163" s="26" t="s">
+      <c r="B163" s="24" t="s">
         <v>2490</v>
       </c>
-      <c r="C163" s="10" t="s">
+      <c r="C163" s="8" t="s">
         <v>2192</v>
       </c>
-      <c r="D163" s="23" t="s">
+      <c r="D163" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E163" s="18">
+      <c r="E163" s="16">
         <v>44211</v>
       </c>
-      <c r="F163" s="19">
+      <c r="F163" s="17">
         <v>44392</v>
       </c>
-      <c r="G163" s="9" t="s">
+      <c r="G163" s="7" t="s">
         <v>2491</v>
       </c>
-      <c r="H163" s="9" t="s">
+      <c r="H163" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I163" s="9" t="s">
+      <c r="I163" s="7" t="s">
         <v>1964</v>
       </c>
-      <c r="J163" s="24">
+      <c r="J163" s="22">
         <v>44520</v>
       </c>
     </row>
     <row r="164" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="7">
+      <c r="A164">
         <v>2021</v>
       </c>
-      <c r="B164" s="26" t="s">
+      <c r="B164" s="24" t="s">
         <v>2492</v>
       </c>
-      <c r="C164" s="10" t="s">
+      <c r="C164" s="8" t="s">
         <v>1956</v>
       </c>
-      <c r="D164" s="23" t="s">
+      <c r="D164" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E164" s="18">
+      <c r="E164" s="16">
         <v>43936</v>
       </c>
-      <c r="F164" s="19">
+      <c r="F164" s="17">
         <v>44454</v>
       </c>
-      <c r="G164" s="9" t="s">
+      <c r="G164" s="7" t="s">
         <v>2493</v>
       </c>
-      <c r="H164" s="9" t="s">
+      <c r="H164" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I164" s="9" t="s">
+      <c r="I164" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J164" s="24" t="s">
+      <c r="J164" s="22" t="s">
         <v>2494</v>
       </c>
     </row>
     <row r="165" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="7">
+      <c r="A165">
         <v>2021</v>
       </c>
-      <c r="B165" s="26" t="s">
+      <c r="B165" s="24" t="s">
         <v>2343</v>
       </c>
-      <c r="C165" s="10" t="s">
+      <c r="C165" s="8" t="s">
         <v>2495</v>
       </c>
-      <c r="D165" s="25" t="s">
+      <c r="D165" s="23" t="s">
         <v>2496</v>
       </c>
-      <c r="E165" s="18">
+      <c r="E165" s="16">
         <v>2018</v>
       </c>
-      <c r="F165" s="19">
+      <c r="F165" s="17">
         <v>2022</v>
       </c>
-      <c r="G165" s="9" t="s">
+      <c r="G165" s="7" t="s">
         <v>2497</v>
       </c>
-      <c r="H165" s="9" t="s">
+      <c r="H165" s="7" t="s">
         <v>2479</v>
       </c>
-      <c r="I165" s="9" t="s">
+      <c r="I165" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J165" s="24">
+      <c r="J165" s="22">
         <v>44540</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="7">
+      <c r="A166">
         <v>2021</v>
       </c>
-      <c r="B166" s="26" t="s">
+      <c r="B166" s="24" t="s">
         <v>2343</v>
       </c>
-      <c r="C166" s="9" t="s">
+      <c r="C166" s="7" t="s">
         <v>2498</v>
       </c>
-      <c r="D166" s="25" t="s">
+      <c r="D166" s="23" t="s">
         <v>2496</v>
       </c>
-      <c r="E166" s="18">
+      <c r="E166" s="16">
         <v>2018</v>
       </c>
-      <c r="F166" s="19">
+      <c r="F166" s="17">
         <v>2022</v>
       </c>
-      <c r="G166" s="9" t="s">
+      <c r="G166" s="7" t="s">
         <v>2499</v>
       </c>
-      <c r="H166" s="9" t="s">
+      <c r="H166" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I166" s="9" t="s">
+      <c r="I166" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J166" s="24" t="s">
+      <c r="J166" s="22" t="s">
         <v>2500</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="7">
+      <c r="A167">
         <v>2021</v>
       </c>
-      <c r="B167" s="26" t="s">
+      <c r="B167" s="24" t="s">
         <v>2501</v>
       </c>
-      <c r="C167" s="10" t="s">
+      <c r="C167" s="8" t="s">
         <v>2146</v>
       </c>
-      <c r="D167" s="23" t="s">
+      <c r="D167" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E167" s="18">
+      <c r="E167" s="16">
         <v>44044</v>
       </c>
-      <c r="F167" s="19">
+      <c r="F167" s="17">
         <v>44378</v>
       </c>
-      <c r="G167" s="9" t="s">
+      <c r="G167" s="7" t="s">
         <v>2502</v>
       </c>
-      <c r="H167" s="9" t="s">
+      <c r="H167" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I167" s="9" t="s">
+      <c r="I167" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J167" s="24" t="s">
+      <c r="J167" s="22" t="s">
         <v>2503</v>
       </c>
     </row>
     <row r="168" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="7">
+      <c r="A168">
         <v>2021</v>
       </c>
-      <c r="B168" s="26" t="s">
+      <c r="B168" s="24" t="s">
         <v>2504</v>
       </c>
-      <c r="C168" s="10" t="s">
+      <c r="C168" s="8" t="s">
         <v>1956</v>
       </c>
-      <c r="D168" s="23" t="s">
+      <c r="D168" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E168" s="18">
+      <c r="E168" s="16">
         <v>44306</v>
       </c>
-      <c r="F168" s="19">
+      <c r="F168" s="17">
         <v>44459</v>
       </c>
-      <c r="G168" s="9" t="s">
+      <c r="G168" s="7" t="s">
         <v>2502</v>
       </c>
-      <c r="H168" s="9" t="s">
+      <c r="H168" s="7" t="s">
         <v>2215</v>
       </c>
-      <c r="I168" s="9" t="s">
+      <c r="I168" s="7" t="s">
         <v>1954</v>
       </c>
-      <c r="J168" s="24" t="s">
+      <c r="J168" s="22" t="s">
         <v>2503</v>
       </c>
     </row>
     <row r="169" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="7">
+      <c r="A169">
         <v>2021</v>
       </c>
-      <c r="B169" s="26" t="s">
+      <c r="B169" s="24" t="s">
         <v>2505</v>
       </c>
-      <c r="C169" s="10" t="s">
+      <c r="C169" s="8" t="s">
         <v>2131</v>
       </c>
-      <c r="D169" s="23" t="s">
+      <c r="D169" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E169" s="18">
+      <c r="E169" s="16">
         <v>44211</v>
       </c>
-      <c r="F169" s="19">
+      <c r="F169" s="17">
         <v>44454</v>
       </c>
-      <c r="G169" s="9" t="s">
+      <c r="G169" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H169" s="9" t="s">
+      <c r="H169" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I169" s="9" t="s">
+      <c r="I169" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J169" s="24" t="s">
+      <c r="J169" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="170" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="7">
+      <c r="A170">
         <v>2021</v>
       </c>
-      <c r="B170" s="26" t="s">
+      <c r="B170" s="24" t="s">
         <v>2508</v>
       </c>
-      <c r="C170" s="10" t="s">
+      <c r="C170" s="8" t="s">
         <v>2509</v>
       </c>
-      <c r="D170" s="23" t="s">
+      <c r="D170" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E170" s="18">
+      <c r="E170" s="16">
         <v>44256</v>
       </c>
-      <c r="F170" s="22">
+      <c r="F170" s="20">
         <v>44378</v>
       </c>
-      <c r="G170" s="9" t="s">
+      <c r="G170" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H170" s="9" t="s">
+      <c r="H170" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I170" s="9" t="s">
+      <c r="I170" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J170" s="24" t="s">
+      <c r="J170" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="171" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="7">
+      <c r="A171">
         <v>2021</v>
       </c>
-      <c r="B171" s="26" t="s">
+      <c r="B171" s="24" t="s">
         <v>2510</v>
       </c>
-      <c r="C171" s="10" t="s">
+      <c r="C171" s="8" t="s">
         <v>2067</v>
       </c>
-      <c r="D171" s="23" t="s">
+      <c r="D171" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E171" s="18">
+      <c r="E171" s="16">
         <v>44256</v>
       </c>
-      <c r="F171" s="22">
+      <c r="F171" s="20">
         <v>44378</v>
       </c>
-      <c r="G171" s="9" t="s">
+      <c r="G171" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H171" s="9" t="s">
+      <c r="H171" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I171" s="9" t="s">
+      <c r="I171" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J171" s="24" t="s">
+      <c r="J171" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="172" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="7">
+      <c r="A172">
         <v>2021</v>
       </c>
-      <c r="B172" s="26" t="s">
+      <c r="B172" s="24" t="s">
         <v>2511</v>
       </c>
-      <c r="C172" s="10" t="s">
+      <c r="C172" s="8" t="s">
         <v>2336</v>
       </c>
-      <c r="D172" s="23" t="s">
+      <c r="D172" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E172" s="18">
+      <c r="E172" s="16">
         <v>44287</v>
       </c>
-      <c r="F172" s="22">
+      <c r="F172" s="20">
         <v>44378</v>
       </c>
-      <c r="G172" s="9" t="s">
+      <c r="G172" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H172" s="9" t="s">
+      <c r="H172" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I172" s="9" t="s">
+      <c r="I172" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J172" s="24" t="s">
+      <c r="J172" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="173" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="7">
+      <c r="A173">
         <v>2021</v>
       </c>
-      <c r="B173" s="26" t="s">
+      <c r="B173" s="24" t="s">
         <v>2512</v>
       </c>
-      <c r="C173" s="9" t="s">
+      <c r="C173" s="7" t="s">
         <v>2513</v>
       </c>
-      <c r="D173" s="23" t="s">
+      <c r="D173" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E173" s="18">
+      <c r="E173" s="16">
         <v>44256</v>
       </c>
-      <c r="F173" s="19">
+      <c r="F173" s="17">
         <v>44409</v>
       </c>
-      <c r="G173" s="9" t="s">
+      <c r="G173" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H173" s="9" t="s">
+      <c r="H173" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I173" s="9" t="s">
+      <c r="I173" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J173" s="24" t="s">
+      <c r="J173" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="174" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="7">
+      <c r="A174">
         <v>2021</v>
       </c>
-      <c r="B174" s="26" t="s">
+      <c r="B174" s="24" t="s">
         <v>2514</v>
       </c>
-      <c r="C174" s="9" t="s">
+      <c r="C174" s="7" t="s">
         <v>2515</v>
       </c>
-      <c r="D174" s="23" t="s">
+      <c r="D174" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E174" s="18">
+      <c r="E174" s="16">
         <v>44105</v>
       </c>
-      <c r="F174" s="19">
+      <c r="F174" s="17">
         <v>44470</v>
       </c>
-      <c r="G174" s="9" t="s">
+      <c r="G174" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H174" s="9" t="s">
+      <c r="H174" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I174" s="9" t="s">
+      <c r="I174" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J174" s="24" t="s">
+      <c r="J174" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="175" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="7">
+      <c r="A175">
         <v>2021</v>
       </c>
-      <c r="B175" s="26" t="s">
+      <c r="B175" s="24" t="s">
         <v>2516</v>
       </c>
-      <c r="C175" s="9" t="s">
+      <c r="C175" s="7" t="s">
         <v>2517</v>
       </c>
-      <c r="D175" s="23" t="s">
+      <c r="D175" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E175" s="18">
+      <c r="E175" s="16">
         <v>44197</v>
       </c>
-      <c r="F175" s="19">
+      <c r="F175" s="17">
         <v>44440</v>
       </c>
-      <c r="G175" s="9" t="s">
+      <c r="G175" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H175" s="9" t="s">
+      <c r="H175" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I175" s="9" t="s">
+      <c r="I175" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J175" s="24" t="s">
+      <c r="J175" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="176" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="7">
+      <c r="A176">
         <v>2021</v>
       </c>
-      <c r="B176" s="26" t="s">
+      <c r="B176" s="24" t="s">
         <v>2518</v>
       </c>
-      <c r="C176" s="9" t="s">
+      <c r="C176" s="7" t="s">
         <v>2519</v>
       </c>
-      <c r="D176" s="23" t="s">
+      <c r="D176" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E176" s="18">
+      <c r="E176" s="16">
         <v>44317</v>
       </c>
-      <c r="F176" s="19">
+      <c r="F176" s="17">
         <v>44470</v>
       </c>
-      <c r="G176" s="9" t="s">
+      <c r="G176" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H176" s="9" t="s">
+      <c r="H176" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I176" s="9" t="s">
+      <c r="I176" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J176" s="24" t="s">
+      <c r="J176" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="177" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="7">
+      <c r="A177">
         <v>2021</v>
       </c>
-      <c r="B177" s="26" t="s">
+      <c r="B177" s="24" t="s">
         <v>2520</v>
       </c>
-      <c r="C177" s="9" t="s">
+      <c r="C177" s="7" t="s">
         <v>2517</v>
       </c>
-      <c r="D177" s="23" t="s">
+      <c r="D177" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E177" s="18">
+      <c r="E177" s="16">
         <v>44256</v>
       </c>
-      <c r="F177" s="19">
+      <c r="F177" s="17">
         <v>44378</v>
       </c>
-      <c r="G177" s="9" t="s">
+      <c r="G177" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H177" s="9" t="s">
+      <c r="H177" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I177" s="9" t="s">
+      <c r="I177" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J177" s="24" t="s">
+      <c r="J177" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="178" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="7">
+      <c r="A178">
         <v>2021</v>
       </c>
-      <c r="B178" s="26" t="s">
+      <c r="B178" s="24" t="s">
         <v>2521</v>
       </c>
-      <c r="C178" s="9" t="s">
+      <c r="C178" s="7" t="s">
         <v>2522</v>
       </c>
-      <c r="D178" s="23" t="s">
+      <c r="D178" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E178" s="18">
+      <c r="E178" s="16">
         <v>44228</v>
       </c>
-      <c r="F178" s="19">
+      <c r="F178" s="17">
         <v>44378</v>
       </c>
-      <c r="G178" s="9" t="s">
+      <c r="G178" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H178" s="9" t="s">
+      <c r="H178" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I178" s="9" t="s">
+      <c r="I178" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J178" s="24" t="s">
+      <c r="J178" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="179" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="7">
+      <c r="A179">
         <v>2021</v>
       </c>
-      <c r="B179" s="26" t="s">
+      <c r="B179" s="24" t="s">
         <v>2523</v>
       </c>
-      <c r="C179" s="9" t="s">
+      <c r="C179" s="7" t="s">
         <v>2524</v>
       </c>
-      <c r="D179" s="23" t="s">
+      <c r="D179" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E179" s="18">
+      <c r="E179" s="16">
         <v>44197</v>
       </c>
-      <c r="F179" s="19">
+      <c r="F179" s="17">
         <v>44378</v>
       </c>
-      <c r="G179" s="9" t="s">
+      <c r="G179" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H179" s="9" t="s">
+      <c r="H179" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I179" s="9" t="s">
+      <c r="I179" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J179" s="24" t="s">
+      <c r="J179" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="180" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="7">
+      <c r="A180">
         <v>2021</v>
       </c>
-      <c r="B180" s="26" t="s">
+      <c r="B180" s="24" t="s">
         <v>2525</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C180" s="8" t="s">
         <v>2526</v>
       </c>
-      <c r="D180" s="23" t="s">
+      <c r="D180" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E180" s="18">
+      <c r="E180" s="16">
         <v>44228</v>
       </c>
-      <c r="F180" s="19">
+      <c r="F180" s="17">
         <v>44409</v>
       </c>
-      <c r="G180" s="9" t="s">
+      <c r="G180" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H180" s="9" t="s">
+      <c r="H180" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I180" s="9" t="s">
+      <c r="I180" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J180" s="24" t="s">
+      <c r="J180" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
     <row r="181" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="7">
+      <c r="A181">
         <v>2021</v>
       </c>
-      <c r="B181" s="20" t="s">
+      <c r="B181" s="18" t="s">
         <v>2527</v>
       </c>
-      <c r="C181" s="9" t="s">
+      <c r="C181" s="7" t="s">
         <v>2528</v>
       </c>
-      <c r="D181" s="23" t="s">
+      <c r="D181" s="21" t="s">
         <v>1951</v>
       </c>
-      <c r="E181" s="18">
+      <c r="E181" s="16">
         <v>44287</v>
       </c>
-      <c r="F181" s="19">
+      <c r="F181" s="17">
         <v>44409</v>
       </c>
-      <c r="G181" s="9" t="s">
+      <c r="G181" s="7" t="s">
         <v>2506</v>
       </c>
-      <c r="H181" s="9" t="s">
+      <c r="H181" s="7" t="s">
         <v>2426</v>
       </c>
-      <c r="I181" s="9" t="s">
+      <c r="I181" s="7" t="s">
         <v>2038</v>
       </c>
-      <c r="J181" s="24" t="s">
+      <c r="J181" s="22" t="s">
         <v>2507</v>
       </c>
     </row>
